--- a/research/traditional_assets/database/data/austria/austria_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_oil_gas_production_and_exploration.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="xtra_o2c" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06309999999999999</v>
+        <v>-0.0351</v>
+      </c>
+      <c r="E2">
+        <v>-0.175</v>
       </c>
       <c r="G2">
-        <v>0.2208316511909568</v>
+        <v>0.1281186783546864</v>
       </c>
       <c r="H2">
-        <v>0.2208316511909568</v>
+        <v>0.1281186783546864</v>
       </c>
       <c r="I2">
-        <v>-0.001033508276140493</v>
+        <v>0.04012137559002023</v>
       </c>
       <c r="J2">
-        <v>-0.001033508276140493</v>
+        <v>0.02760262943597567</v>
       </c>
       <c r="K2">
-        <v>-8.75</v>
+        <v>10.9</v>
       </c>
       <c r="L2">
-        <v>-0.03532498990714574</v>
+        <v>0.03674983142279164</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>134.9</v>
+        <v>165</v>
       </c>
       <c r="V2">
-        <v>1.10392798690671</v>
+        <v>1.505474452554745</v>
       </c>
       <c r="W2">
-        <v>-0.04075454122030741</v>
+        <v>0.04712494595763078</v>
       </c>
       <c r="X2">
-        <v>0.1156149813006719</v>
+        <v>0.1887289968543005</v>
       </c>
       <c r="Y2">
-        <v>-0.1563695225209793</v>
+        <v>-0.1416040508966697</v>
       </c>
       <c r="Z2">
-        <v>1.069516407599309</v>
+        <v>1.159046502540055</v>
       </c>
       <c r="AA2">
-        <v>-0.001105354058721934</v>
+        <v>0.03199273110867676</v>
       </c>
       <c r="AB2">
-        <v>0.06556776632205345</v>
+        <v>0.1098708257114028</v>
       </c>
       <c r="AC2">
-        <v>-0.06667312038077539</v>
+        <v>-0.07787809460272609</v>
       </c>
       <c r="AD2">
-        <v>145.4</v>
+        <v>134.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>145.4</v>
+        <v>134.3</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>-30.69999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5433482810164424</v>
+        <v>0.5506355063550635</v>
       </c>
       <c r="AI2">
-        <v>0.3842494714587738</v>
+        <v>0.2654150197628459</v>
       </c>
       <c r="AJ2">
-        <v>0.07912584777694047</v>
+        <v>-0.3891001267427121</v>
       </c>
       <c r="AK2">
-        <v>0.0431211498973306</v>
+        <v>-0.09002932551319645</v>
       </c>
       <c r="AL2">
-        <v>4.01</v>
+        <v>3.17</v>
       </c>
       <c r="AM2">
-        <v>-0.5300000000000002</v>
+        <v>-4.98</v>
       </c>
       <c r="AN2">
-        <v>5.52851711026616</v>
+        <v>3.059225512528474</v>
       </c>
       <c r="AO2">
-        <v>-0.06384039900249378</v>
+        <v>3.753943217665615</v>
       </c>
       <c r="AP2">
-        <v>0.3992395437262357</v>
+        <v>-0.6993166287015943</v>
       </c>
       <c r="AQ2">
-        <v>0.4830188679245281</v>
+        <v>-2.389558232931727</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06309999999999999</v>
+        <v>-0.0351</v>
+      </c>
+      <c r="E3">
+        <v>-0.175</v>
       </c>
       <c r="G3">
-        <v>0.2208316511909568</v>
+        <v>0.1281186783546864</v>
       </c>
       <c r="H3">
-        <v>0.2208316511909568</v>
+        <v>0.1281186783546864</v>
       </c>
       <c r="I3">
-        <v>-0.001033508276140493</v>
+        <v>0.04012137559002023</v>
       </c>
       <c r="J3">
-        <v>-0.001033508276140493</v>
+        <v>0.02760262943597567</v>
       </c>
       <c r="K3">
-        <v>-8.75</v>
+        <v>10.9</v>
       </c>
       <c r="L3">
-        <v>-0.03532498990714574</v>
+        <v>0.03674983142279164</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>134.9</v>
+        <v>165</v>
       </c>
       <c r="V3">
-        <v>1.10392798690671</v>
+        <v>1.505474452554745</v>
       </c>
       <c r="W3">
-        <v>-0.04075454122030741</v>
+        <v>0.04712494595763078</v>
       </c>
       <c r="X3">
-        <v>0.1156149813006719</v>
+        <v>0.1887289968543005</v>
       </c>
       <c r="Y3">
-        <v>-0.1563695225209793</v>
+        <v>-0.1416040508966697</v>
       </c>
       <c r="Z3">
-        <v>1.069516407599309</v>
+        <v>1.159046502540055</v>
       </c>
       <c r="AA3">
-        <v>-0.001105354058721934</v>
+        <v>0.03199273110867676</v>
       </c>
       <c r="AB3">
-        <v>0.06556776632205345</v>
+        <v>0.1098708257114028</v>
       </c>
       <c r="AC3">
-        <v>-0.06667312038077539</v>
+        <v>-0.07787809460272609</v>
       </c>
       <c r="AD3">
-        <v>145.4</v>
+        <v>134.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>145.4</v>
+        <v>134.3</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>-30.69999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5433482810164424</v>
+        <v>0.5506355063550635</v>
       </c>
       <c r="AI3">
-        <v>0.3842494714587738</v>
+        <v>0.2654150197628459</v>
       </c>
       <c r="AJ3">
-        <v>0.07912584777694047</v>
+        <v>-0.3891001267427121</v>
       </c>
       <c r="AK3">
-        <v>0.0431211498973306</v>
+        <v>-0.09002932551319645</v>
       </c>
       <c r="AL3">
-        <v>4.01</v>
+        <v>3.17</v>
       </c>
       <c r="AM3">
-        <v>-0.5300000000000002</v>
+        <v>-4.98</v>
       </c>
       <c r="AN3">
-        <v>5.52851711026616</v>
+        <v>3.059225512528474</v>
       </c>
       <c r="AO3">
-        <v>-0.06384039900249378</v>
+        <v>3.753943217665615</v>
       </c>
       <c r="AP3">
-        <v>0.3992395437262357</v>
+        <v>-0.6993166287015943</v>
       </c>
       <c r="AQ3">
-        <v>0.4830188679245281</v>
+        <v>-2.389558232931727</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Petro Welt Technologies AG (XTRA:O2C)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>XTRA:O2C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas (Production and Exploration)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.550635506355064</v>
+      </c>
+      <c r="F2">
+        <v>0.19</v>
+      </c>
+      <c r="G2">
+        <v>109.6</v>
+      </c>
+      <c r="H2">
+        <v>193.763965342311</v>
+      </c>
+      <c r="I2">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="J2">
+        <v>75.10496534231071</v>
+      </c>
+      <c r="K2">
+        <v>134.3</v>
+      </c>
+      <c r="L2">
+        <v>46.341</v>
+      </c>
+      <c r="M2">
+        <v>0.109870825711403</v>
+      </c>
+      <c r="N2">
+        <v>0.113462016327044</v>
+      </c>
+      <c r="O2">
+        <v>0.0455159816513761</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.188728996854301</v>
+      </c>
+      <c r="T2">
+        <v>0.130271625095116</v>
+      </c>
+      <c r="U2">
+        <v>2.2702899502286</v>
+      </c>
+      <c r="V2">
+        <v>1.38510305238906</v>
+      </c>
+      <c r="W2">
+        <v>4.66894621099321</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>109.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.0660395809086869</v>
+      </c>
+      <c r="AC2">
+        <v>0.0598894495412844</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>43.9</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>134.3</v>
+      </c>
+      <c r="AK2">
+        <v>134.3</v>
+      </c>
+      <c r="AL2">
+        <v>3.17</v>
+      </c>
+      <c r="AM2">
+        <v>134.3</v>
+      </c>
+      <c r="AN2">
+        <v>165</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1164320372244805</v>
+      </c>
+      <c r="C2">
+        <v>237.2316243281765</v>
+      </c>
+      <c r="D2">
+        <v>72.23162432817645</v>
+      </c>
+      <c r="E2">
+        <v>-134.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>165</v>
+      </c>
+      <c r="H2">
+        <v>109.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>43.9</v>
+      </c>
+      <c r="K2">
+        <v>32</v>
+      </c>
+      <c r="L2">
+        <v>11.9</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>11.9</v>
+      </c>
+      <c r="O2">
+        <v>2.855999999999999</v>
+      </c>
+      <c r="P2">
+        <v>9.043999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>41.044</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1164320372244805</v>
+      </c>
+      <c r="T2">
+        <v>1.175538005485263</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1162050403351417</v>
+      </c>
+      <c r="C3">
+        <v>235.0044497333877</v>
+      </c>
+      <c r="D3">
+        <v>72.44344973338768</v>
+      </c>
+      <c r="E3">
+        <v>-131.861</v>
+      </c>
+      <c r="F3">
+        <v>2.439</v>
+      </c>
+      <c r="G3">
+        <v>165</v>
+      </c>
+      <c r="H3">
+        <v>109.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>43.9</v>
+      </c>
+      <c r="K3">
+        <v>32</v>
+      </c>
+      <c r="L3">
+        <v>11.9</v>
+      </c>
+      <c r="M3">
+        <v>0.1114623</v>
+      </c>
+      <c r="N3">
+        <v>11.7885377</v>
+      </c>
+      <c r="O3">
+        <v>2.829249048</v>
+      </c>
+      <c r="P3">
+        <v>8.959288652</v>
+      </c>
+      <c r="Q3">
+        <v>40.959288652</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.117028000338527</v>
+      </c>
+      <c r="T3">
+        <v>1.184562337648585</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>106.7625555905449</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.115978043445803</v>
+      </c>
+      <c r="C4">
+        <v>232.7785211849074</v>
+      </c>
+      <c r="D4">
+        <v>72.65652118490738</v>
+      </c>
+      <c r="E4">
+        <v>-129.422</v>
+      </c>
+      <c r="F4">
+        <v>4.878</v>
+      </c>
+      <c r="G4">
+        <v>165</v>
+      </c>
+      <c r="H4">
+        <v>109.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>43.9</v>
+      </c>
+      <c r="K4">
+        <v>32</v>
+      </c>
+      <c r="L4">
+        <v>11.9</v>
+      </c>
+      <c r="M4">
+        <v>0.2229246</v>
+      </c>
+      <c r="N4">
+        <v>11.6770754</v>
+      </c>
+      <c r="O4">
+        <v>2.802498095999999</v>
+      </c>
+      <c r="P4">
+        <v>8.874577303999999</v>
+      </c>
+      <c r="Q4">
+        <v>40.874577304</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1176361259651051</v>
+      </c>
+      <c r="T4">
+        <v>1.193770839856055</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>53.38127779527247</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1157510465564642</v>
+      </c>
+      <c r="C5">
+        <v>230.5538497098229</v>
+      </c>
+      <c r="D5">
+        <v>72.87084970982286</v>
+      </c>
+      <c r="E5">
+        <v>-126.983</v>
+      </c>
+      <c r="F5">
+        <v>7.317</v>
+      </c>
+      <c r="G5">
+        <v>165</v>
+      </c>
+      <c r="H5">
+        <v>109.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>43.9</v>
+      </c>
+      <c r="K5">
+        <v>32</v>
+      </c>
+      <c r="L5">
+        <v>11.9</v>
+      </c>
+      <c r="M5">
+        <v>0.3343869</v>
+      </c>
+      <c r="N5">
+        <v>11.5656131</v>
+      </c>
+      <c r="O5">
+        <v>2.775747143999999</v>
+      </c>
+      <c r="P5">
+        <v>8.789865956</v>
+      </c>
+      <c r="Q5">
+        <v>40.789865956</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1182567902643961</v>
+      </c>
+      <c r="T5">
+        <v>1.203169208088422</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>35.58751853018165</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1155240496671255</v>
+      </c>
+      <c r="C6">
+        <v>228.330446465721</v>
+      </c>
+      <c r="D6">
+        <v>73.086446465721</v>
+      </c>
+      <c r="E6">
+        <v>-124.544</v>
+      </c>
+      <c r="F6">
+        <v>9.756</v>
+      </c>
+      <c r="G6">
+        <v>165</v>
+      </c>
+      <c r="H6">
+        <v>109.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>43.9</v>
+      </c>
+      <c r="K6">
+        <v>32</v>
+      </c>
+      <c r="L6">
+        <v>11.9</v>
+      </c>
+      <c r="M6">
+        <v>0.4458492000000001</v>
+      </c>
+      <c r="N6">
+        <v>11.4541508</v>
+      </c>
+      <c r="O6">
+        <v>2.748996191999999</v>
+      </c>
+      <c r="P6">
+        <v>8.705154607999999</v>
+      </c>
+      <c r="Q6">
+        <v>40.705154608</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1188903850699224</v>
+      </c>
+      <c r="T6">
+        <v>1.212763375658963</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>26.69063889763624</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1152970527777867</v>
+      </c>
+      <c r="C7">
+        <v>226.1083227426246</v>
+      </c>
+      <c r="D7">
+        <v>73.30332274262457</v>
+      </c>
+      <c r="E7">
+        <v>-122.105</v>
+      </c>
+      <c r="F7">
+        <v>12.195</v>
+      </c>
+      <c r="G7">
+        <v>165</v>
+      </c>
+      <c r="H7">
+        <v>109.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>43.9</v>
+      </c>
+      <c r="K7">
+        <v>32</v>
+      </c>
+      <c r="L7">
+        <v>11.9</v>
+      </c>
+      <c r="M7">
+        <v>0.5573115000000001</v>
+      </c>
+      <c r="N7">
+        <v>11.3426885</v>
+      </c>
+      <c r="O7">
+        <v>2.722245239999999</v>
+      </c>
+      <c r="P7">
+        <v>8.620443259999998</v>
+      </c>
+      <c r="Q7">
+        <v>40.62044326</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1195373187134597</v>
+      </c>
+      <c r="T7">
+        <v>1.222559525704674</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>21.35251111810899</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.115070055888448</v>
+      </c>
+      <c r="C8">
+        <v>223.8874899649629</v>
+      </c>
+      <c r="D8">
+        <v>73.52148996496288</v>
+      </c>
+      <c r="E8">
+        <v>-119.666</v>
+      </c>
+      <c r="F8">
+        <v>14.634</v>
+      </c>
+      <c r="G8">
+        <v>165</v>
+      </c>
+      <c r="H8">
+        <v>109.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>43.9</v>
+      </c>
+      <c r="K8">
+        <v>32</v>
+      </c>
+      <c r="L8">
+        <v>11.9</v>
+      </c>
+      <c r="M8">
+        <v>0.6687738000000001</v>
+      </c>
+      <c r="N8">
+        <v>11.2312262</v>
+      </c>
+      <c r="O8">
+        <v>2.695494287999999</v>
+      </c>
+      <c r="P8">
+        <v>8.535731911999999</v>
+      </c>
+      <c r="Q8">
+        <v>40.535731912</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1201980169026042</v>
+      </c>
+      <c r="T8">
+        <v>1.232564104474761</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>17.79375926509082</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1148430589991092</v>
+      </c>
+      <c r="C9">
+        <v>221.667959693578</v>
+      </c>
+      <c r="D9">
+        <v>73.74095969357799</v>
+      </c>
+      <c r="E9">
+        <v>-117.227</v>
+      </c>
+      <c r="F9">
+        <v>17.073</v>
+      </c>
+      <c r="G9">
+        <v>165</v>
+      </c>
+      <c r="H9">
+        <v>109.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>43.9</v>
+      </c>
+      <c r="K9">
+        <v>32</v>
+      </c>
+      <c r="L9">
+        <v>11.9</v>
+      </c>
+      <c r="M9">
+        <v>0.7802361000000001</v>
+      </c>
+      <c r="N9">
+        <v>11.1197639</v>
+      </c>
+      <c r="O9">
+        <v>2.668743335999999</v>
+      </c>
+      <c r="P9">
+        <v>8.451020564</v>
+      </c>
+      <c r="Q9">
+        <v>40.451020564</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1208729236549561</v>
+      </c>
+      <c r="T9">
+        <v>1.242783835476463</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.25179365579213</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1146160621097704</v>
+      </c>
+      <c r="C10">
+        <v>219.4497436277668</v>
+      </c>
+      <c r="D10">
+        <v>73.96174362776678</v>
+      </c>
+      <c r="E10">
+        <v>-114.788</v>
+      </c>
+      <c r="F10">
+        <v>19.512</v>
+      </c>
+      <c r="G10">
+        <v>165</v>
+      </c>
+      <c r="H10">
+        <v>109.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>43.9</v>
+      </c>
+      <c r="K10">
+        <v>32</v>
+      </c>
+      <c r="L10">
+        <v>11.9</v>
+      </c>
+      <c r="M10">
+        <v>0.8916984000000001</v>
+      </c>
+      <c r="N10">
+        <v>11.0083016</v>
+      </c>
+      <c r="O10">
+        <v>2.641992384</v>
+      </c>
+      <c r="P10">
+        <v>8.366309215999999</v>
+      </c>
+      <c r="Q10">
+        <v>40.366309216</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1215625022932287</v>
+      </c>
+      <c r="T10">
+        <v>1.25322573454342</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.34531944881812</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1144985052204317</v>
+      </c>
+      <c r="C11">
+        <v>217.125603392641</v>
+      </c>
+      <c r="D11">
+        <v>74.07660339264102</v>
+      </c>
+      <c r="E11">
+        <v>-112.349</v>
+      </c>
+      <c r="F11">
+        <v>21.951</v>
+      </c>
+      <c r="G11">
+        <v>165</v>
+      </c>
+      <c r="H11">
+        <v>109.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>43.9</v>
+      </c>
+      <c r="K11">
+        <v>32</v>
+      </c>
+      <c r="L11">
+        <v>11.9</v>
+      </c>
+      <c r="M11">
+        <v>1.0382823</v>
+      </c>
+      <c r="N11">
+        <v>10.8617177</v>
+      </c>
+      <c r="O11">
+        <v>2.606812247999999</v>
+      </c>
+      <c r="P11">
+        <v>8.254905451999999</v>
+      </c>
+      <c r="Q11">
+        <v>40.254905452</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1222672365059689</v>
+      </c>
+      <c r="T11">
+        <v>1.263897125897562</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.035948</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.46123746884638</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.114283668331093</v>
+      </c>
+      <c r="C12">
+        <v>214.897435581875</v>
+      </c>
+      <c r="D12">
+        <v>74.28743558187499</v>
+      </c>
+      <c r="E12">
+        <v>-109.91</v>
+      </c>
+      <c r="F12">
+        <v>24.39</v>
+      </c>
+      <c r="G12">
+        <v>165</v>
+      </c>
+      <c r="H12">
+        <v>109.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>43.9</v>
+      </c>
+      <c r="K12">
+        <v>32</v>
+      </c>
+      <c r="L12">
+        <v>11.9</v>
+      </c>
+      <c r="M12">
+        <v>1.153647</v>
+      </c>
+      <c r="N12">
+        <v>10.746353</v>
+      </c>
+      <c r="O12">
+        <v>2.57912472</v>
+      </c>
+      <c r="P12">
+        <v>8.16722828</v>
+      </c>
+      <c r="Q12">
+        <v>40.16722828</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1229876314789922</v>
+      </c>
+      <c r="T12">
+        <v>1.274805659281797</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.035948</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.31511372196174</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1143865114417542</v>
+      </c>
+      <c r="C13">
+        <v>212.3573599956022</v>
+      </c>
+      <c r="D13">
+        <v>74.18635999560225</v>
+      </c>
+      <c r="E13">
+        <v>-107.471</v>
+      </c>
+      <c r="F13">
+        <v>26.829</v>
+      </c>
+      <c r="G13">
+        <v>165</v>
+      </c>
+      <c r="H13">
+        <v>109.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>43.9</v>
+      </c>
+      <c r="K13">
+        <v>32</v>
+      </c>
+      <c r="L13">
+        <v>11.9</v>
+      </c>
+      <c r="M13">
+        <v>1.3709619</v>
+      </c>
+      <c r="N13">
+        <v>10.5290381</v>
+      </c>
+      <c r="O13">
+        <v>2.526969144</v>
+      </c>
+      <c r="P13">
+        <v>8.002068955999999</v>
+      </c>
+      <c r="Q13">
+        <v>40.002068956</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1237242151030946</v>
+      </c>
+      <c r="T13">
+        <v>1.285959328247699</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.038836</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.680036987169373</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1142005545524154</v>
+      </c>
+      <c r="C14">
+        <v>210.1013223732404</v>
+      </c>
+      <c r="D14">
+        <v>74.36932237324044</v>
+      </c>
+      <c r="E14">
+        <v>-105.032</v>
+      </c>
+      <c r="F14">
+        <v>29.268</v>
+      </c>
+      <c r="G14">
+        <v>165</v>
+      </c>
+      <c r="H14">
+        <v>109.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>43.9</v>
+      </c>
+      <c r="K14">
+        <v>32</v>
+      </c>
+      <c r="L14">
+        <v>11.9</v>
+      </c>
+      <c r="M14">
+        <v>1.4955948</v>
+      </c>
+      <c r="N14">
+        <v>10.4044052</v>
+      </c>
+      <c r="O14">
+        <v>2.497057248</v>
+      </c>
+      <c r="P14">
+        <v>7.907347951999999</v>
+      </c>
+      <c r="Q14">
+        <v>39.907347952</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1244775392641084</v>
+      </c>
+      <c r="T14">
+        <v>1.2973664896901</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.038836</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.956700571571925</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1142023176630767</v>
+      </c>
+      <c r="C15">
+        <v>207.6605834168103</v>
+      </c>
+      <c r="D15">
+        <v>74.36758341681032</v>
+      </c>
+      <c r="E15">
+        <v>-102.593</v>
+      </c>
+      <c r="F15">
+        <v>31.707</v>
+      </c>
+      <c r="G15">
+        <v>165</v>
+      </c>
+      <c r="H15">
+        <v>109.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>43.9</v>
+      </c>
+      <c r="K15">
+        <v>32</v>
+      </c>
+      <c r="L15">
+        <v>11.9</v>
+      </c>
+      <c r="M15">
+        <v>1.680471</v>
+      </c>
+      <c r="N15">
+        <v>10.219529</v>
+      </c>
+      <c r="O15">
+        <v>2.452686959999999</v>
+      </c>
+      <c r="P15">
+        <v>7.766842039999998</v>
+      </c>
+      <c r="Q15">
+        <v>39.76684204</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1252481812219272</v>
+      </c>
+      <c r="T15">
+        <v>1.309035884728877</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.04028</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.081348026832951</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1140308007737379</v>
+      </c>
+      <c r="C16">
+        <v>205.3911322777038</v>
+      </c>
+      <c r="D16">
+        <v>74.53713227770379</v>
+      </c>
+      <c r="E16">
+        <v>-100.154</v>
+      </c>
+      <c r="F16">
+        <v>34.146</v>
+      </c>
+      <c r="G16">
+        <v>165</v>
+      </c>
+      <c r="H16">
+        <v>109.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>43.9</v>
+      </c>
+      <c r="K16">
+        <v>32</v>
+      </c>
+      <c r="L16">
+        <v>11.9</v>
+      </c>
+      <c r="M16">
+        <v>1.809738</v>
+      </c>
+      <c r="N16">
+        <v>10.090262</v>
+      </c>
+      <c r="O16">
+        <v>2.42166288</v>
+      </c>
+      <c r="P16">
+        <v>7.66859912</v>
+      </c>
+      <c r="Q16">
+        <v>39.66859912</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1260367450857418</v>
+      </c>
+      <c r="T16">
+        <v>1.320976661047626</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.04028</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.575537453487741</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1140872838843992</v>
+      </c>
+      <c r="C17">
+        <v>202.8962119565872</v>
+      </c>
+      <c r="D17">
+        <v>74.48121195658717</v>
+      </c>
+      <c r="E17">
+        <v>-97.715</v>
+      </c>
+      <c r="F17">
+        <v>36.585</v>
+      </c>
+      <c r="G17">
+        <v>165</v>
+      </c>
+      <c r="H17">
+        <v>109.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>43.9</v>
+      </c>
+      <c r="K17">
+        <v>32</v>
+      </c>
+      <c r="L17">
+        <v>11.9</v>
+      </c>
+      <c r="M17">
+        <v>2.012175</v>
+      </c>
+      <c r="N17">
+        <v>9.887824999999999</v>
+      </c>
+      <c r="O17">
+        <v>2.373078</v>
+      </c>
+      <c r="P17">
+        <v>7.514747</v>
+      </c>
+      <c r="Q17">
+        <v>39.514747</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1268438633934108</v>
+      </c>
+      <c r="T17">
+        <v>1.333198396809169</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.0418</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.913998533924733</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1139309669950604</v>
+      </c>
+      <c r="C18">
+        <v>200.6121769707869</v>
+      </c>
+      <c r="D18">
+        <v>74.63617697078695</v>
+      </c>
+      <c r="E18">
+        <v>-95.27600000000001</v>
+      </c>
+      <c r="F18">
+        <v>39.024</v>
+      </c>
+      <c r="G18">
+        <v>165</v>
+      </c>
+      <c r="H18">
+        <v>109.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>43.9</v>
+      </c>
+      <c r="K18">
+        <v>32</v>
+      </c>
+      <c r="L18">
+        <v>11.9</v>
+      </c>
+      <c r="M18">
+        <v>2.14632</v>
+      </c>
+      <c r="N18">
+        <v>9.753679999999999</v>
+      </c>
+      <c r="O18">
+        <v>2.3408832</v>
+      </c>
+      <c r="P18">
+        <v>7.412796799999999</v>
+      </c>
+      <c r="Q18">
+        <v>39.4127968</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1276701988036434</v>
+      </c>
+      <c r="T18">
+        <v>1.345711126279321</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.0418</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.544373625554437</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1137746501057217</v>
+      </c>
+      <c r="C19">
+        <v>198.3287881673682</v>
+      </c>
+      <c r="D19">
+        <v>74.7917881673682</v>
+      </c>
+      <c r="E19">
+        <v>-92.83700000000002</v>
+      </c>
+      <c r="F19">
+        <v>41.463</v>
+      </c>
+      <c r="G19">
+        <v>165</v>
+      </c>
+      <c r="H19">
+        <v>109.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>43.9</v>
+      </c>
+      <c r="K19">
+        <v>32</v>
+      </c>
+      <c r="L19">
+        <v>11.9</v>
+      </c>
+      <c r="M19">
+        <v>2.280465</v>
+      </c>
+      <c r="N19">
+        <v>9.619534999999999</v>
+      </c>
+      <c r="O19">
+        <v>2.3086884</v>
+      </c>
+      <c r="P19">
+        <v>7.3108466</v>
+      </c>
+      <c r="Q19">
+        <v>39.3108466</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.128516445910508</v>
+      </c>
+      <c r="T19">
+        <v>1.358525367302969</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.0418</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.218234000521823</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1136183332163829</v>
+      </c>
+      <c r="C20">
+        <v>196.0460495965101</v>
+      </c>
+      <c r="D20">
+        <v>74.94804959651007</v>
+      </c>
+      <c r="E20">
+        <v>-90.39800000000001</v>
+      </c>
+      <c r="F20">
+        <v>43.902</v>
+      </c>
+      <c r="G20">
+        <v>165</v>
+      </c>
+      <c r="H20">
+        <v>109.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>43.9</v>
+      </c>
+      <c r="K20">
+        <v>32</v>
+      </c>
+      <c r="L20">
+        <v>11.9</v>
+      </c>
+      <c r="M20">
+        <v>2.41461</v>
+      </c>
+      <c r="N20">
+        <v>9.485389999999999</v>
+      </c>
+      <c r="O20">
+        <v>2.2764936</v>
+      </c>
+      <c r="P20">
+        <v>7.208896399999999</v>
+      </c>
+      <c r="Q20">
+        <v>39.2088964</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1293833331907109</v>
+      </c>
+      <c r="T20">
+        <v>1.37165215079061</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.0418</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.928332111603943</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1134620163270442</v>
+      </c>
+      <c r="C21">
+        <v>193.7639653423107</v>
+      </c>
+      <c r="D21">
+        <v>75.10496534231066</v>
+      </c>
+      <c r="E21">
+        <v>-87.959</v>
+      </c>
+      <c r="F21">
+        <v>46.341</v>
+      </c>
+      <c r="G21">
+        <v>165</v>
+      </c>
+      <c r="H21">
+        <v>109.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>43.9</v>
+      </c>
+      <c r="K21">
+        <v>32</v>
+      </c>
+      <c r="L21">
+        <v>11.9</v>
+      </c>
+      <c r="M21">
+        <v>2.548755</v>
+      </c>
+      <c r="N21">
+        <v>9.351244999999999</v>
+      </c>
+      <c r="O21">
+        <v>2.2442988</v>
+      </c>
+      <c r="P21">
+        <v>7.106946199999999</v>
+      </c>
+      <c r="Q21">
+        <v>39.1069462</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1302716250951163</v>
+      </c>
+      <c r="T21">
+        <v>1.385103052389056</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.0418</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.66894621099321</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1138832994377054</v>
+      </c>
+      <c r="C22">
+        <v>190.9035606669372</v>
+      </c>
+      <c r="D22">
+        <v>74.68356066693718</v>
+      </c>
+      <c r="E22">
+        <v>-85.52000000000001</v>
+      </c>
+      <c r="F22">
+        <v>48.78</v>
+      </c>
+      <c r="G22">
+        <v>165</v>
+      </c>
+      <c r="H22">
+        <v>109.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>43.9</v>
+      </c>
+      <c r="K22">
+        <v>32</v>
+      </c>
+      <c r="L22">
+        <v>11.9</v>
+      </c>
+      <c r="M22">
+        <v>2.868264</v>
+      </c>
+      <c r="N22">
+        <v>9.031735999999999</v>
+      </c>
+      <c r="O22">
+        <v>2.167616639999999</v>
+      </c>
+      <c r="P22">
+        <v>6.864119359999999</v>
+      </c>
+      <c r="Q22">
+        <v>38.86411936</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1311821242971318</v>
+      </c>
+      <c r="T22">
+        <v>1.398890226527463</v>
+      </c>
+      <c r="U22">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.148851012319646</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1144261825483667</v>
+      </c>
+      <c r="C23">
+        <v>187.9284441744223</v>
+      </c>
+      <c r="D23">
+        <v>74.14744417442226</v>
+      </c>
+      <c r="E23">
+        <v>-83.08100000000002</v>
+      </c>
+      <c r="F23">
+        <v>51.219</v>
+      </c>
+      <c r="G23">
+        <v>165</v>
+      </c>
+      <c r="H23">
+        <v>109.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>43.9</v>
+      </c>
+      <c r="K23">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>11.9</v>
+      </c>
+      <c r="M23">
+        <v>3.226797</v>
+      </c>
+      <c r="N23">
+        <v>8.673202999999999</v>
+      </c>
+      <c r="O23">
+        <v>2.08156872</v>
+      </c>
+      <c r="P23">
+        <v>6.591634279999999</v>
+      </c>
+      <c r="Q23">
+        <v>38.59163428</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1321156741118565</v>
+      </c>
+      <c r="T23">
+        <v>1.413026443049122</v>
+      </c>
+      <c r="U23">
+        <v>0.063</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.04788</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.687867566506353</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1143306656590279</v>
+      </c>
+      <c r="C24">
+        <v>185.5832118270461</v>
+      </c>
+      <c r="D24">
+        <v>74.24121182704604</v>
+      </c>
+      <c r="E24">
+        <v>-80.64200000000001</v>
+      </c>
+      <c r="F24">
+        <v>53.658</v>
+      </c>
+      <c r="G24">
+        <v>165</v>
+      </c>
+      <c r="H24">
+        <v>109.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>43.9</v>
+      </c>
+      <c r="K24">
+        <v>32</v>
+      </c>
+      <c r="L24">
+        <v>11.9</v>
+      </c>
+      <c r="M24">
+        <v>3.380454</v>
+      </c>
+      <c r="N24">
+        <v>8.519545999999998</v>
+      </c>
+      <c r="O24">
+        <v>2.04469104</v>
+      </c>
+      <c r="P24">
+        <v>6.474854959999998</v>
+      </c>
+      <c r="Q24">
+        <v>38.47485496</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1330731611013178</v>
+      </c>
+      <c r="T24">
+        <v>1.427525126661079</v>
+      </c>
+      <c r="U24">
+        <v>0.063</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.04788</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.520237222574245</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1154762287696892</v>
+      </c>
+      <c r="C25">
+        <v>182.03502851268</v>
+      </c>
+      <c r="D25">
+        <v>73.13202851268004</v>
+      </c>
+      <c r="E25">
+        <v>-78.203</v>
+      </c>
+      <c r="F25">
+        <v>56.097</v>
+      </c>
+      <c r="G25">
+        <v>165</v>
+      </c>
+      <c r="H25">
+        <v>109.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>43.9</v>
+      </c>
+      <c r="K25">
+        <v>32</v>
+      </c>
+      <c r="L25">
+        <v>11.9</v>
+      </c>
+      <c r="M25">
+        <v>3.9323997</v>
+      </c>
+      <c r="N25">
+        <v>7.967600299999999</v>
+      </c>
+      <c r="O25">
+        <v>1.912224072</v>
+      </c>
+      <c r="P25">
+        <v>6.055376227999999</v>
+      </c>
+      <c r="Q25">
+        <v>38.055376228</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1340555178827132</v>
+      </c>
+      <c r="T25">
+        <v>1.442400399457762</v>
+      </c>
+      <c r="U25">
+        <v>0.0701</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.053276</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.026142027220681</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1193197918803504</v>
+      </c>
+      <c r="C26">
+        <v>176.1051157763822</v>
+      </c>
+      <c r="D26">
+        <v>69.64111577638224</v>
+      </c>
+      <c r="E26">
+        <v>-75.76400000000001</v>
+      </c>
+      <c r="F26">
+        <v>58.536</v>
+      </c>
+      <c r="G26">
+        <v>165</v>
+      </c>
+      <c r="H26">
+        <v>109.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>43.9</v>
+      </c>
+      <c r="K26">
+        <v>32</v>
+      </c>
+      <c r="L26">
+        <v>11.9</v>
+      </c>
+      <c r="M26">
+        <v>5.350190400000001</v>
+      </c>
+      <c r="N26">
+        <v>6.549809599999998</v>
+      </c>
+      <c r="O26">
+        <v>1.571954303999999</v>
+      </c>
+      <c r="P26">
+        <v>4.977855295999999</v>
+      </c>
+      <c r="Q26">
+        <v>36.977855296</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1350637261583558</v>
+      </c>
+      <c r="T26">
+        <v>1.457667126801726</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.224219908136353</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1194401149910117</v>
+      </c>
+      <c r="C27">
+        <v>173.5622042717785</v>
+      </c>
+      <c r="D27">
+        <v>69.53720427177849</v>
+      </c>
+      <c r="E27">
+        <v>-73.32500000000002</v>
+      </c>
+      <c r="F27">
+        <v>60.975</v>
+      </c>
+      <c r="G27">
+        <v>165</v>
+      </c>
+      <c r="H27">
+        <v>109.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>43.9</v>
+      </c>
+      <c r="K27">
+        <v>32</v>
+      </c>
+      <c r="L27">
+        <v>11.9</v>
+      </c>
+      <c r="M27">
+        <v>5.573115</v>
+      </c>
+      <c r="N27">
+        <v>6.326884999999998</v>
+      </c>
+      <c r="O27">
+        <v>1.518452399999999</v>
+      </c>
+      <c r="P27">
+        <v>4.808432599999999</v>
+      </c>
+      <c r="Q27">
+        <v>36.8084326</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1360988199880155</v>
+      </c>
+      <c r="T27">
+        <v>1.473340966874863</v>
+      </c>
+      <c r="U27">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.135251111810899</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1195604381016729</v>
+      </c>
+      <c r="C28">
+        <v>171.0196023978742</v>
+      </c>
+      <c r="D28">
+        <v>69.43360239787418</v>
+      </c>
+      <c r="E28">
+        <v>-70.88600000000001</v>
+      </c>
+      <c r="F28">
+        <v>63.414</v>
+      </c>
+      <c r="G28">
+        <v>165</v>
+      </c>
+      <c r="H28">
+        <v>109.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>43.9</v>
+      </c>
+      <c r="K28">
+        <v>32</v>
+      </c>
+      <c r="L28">
+        <v>11.9</v>
+      </c>
+      <c r="M28">
+        <v>5.7960396</v>
+      </c>
+      <c r="N28">
+        <v>6.103960399999998</v>
+      </c>
+      <c r="O28">
+        <v>1.464950495999999</v>
+      </c>
+      <c r="P28">
+        <v>4.639009903999999</v>
+      </c>
+      <c r="Q28">
+        <v>36.639009904</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.137161889326585</v>
+      </c>
+      <c r="T28">
+        <v>1.489438424247274</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.053126069048941</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1240104812123342</v>
+      </c>
+      <c r="C29">
+        <v>164.9544930319488</v>
+      </c>
+      <c r="D29">
+        <v>65.80749303194881</v>
+      </c>
+      <c r="E29">
+        <v>-68.447</v>
+      </c>
+      <c r="F29">
+        <v>65.85300000000001</v>
+      </c>
+      <c r="G29">
+        <v>165</v>
+      </c>
+      <c r="H29">
+        <v>109.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>43.9</v>
+      </c>
+      <c r="K29">
+        <v>32</v>
+      </c>
+      <c r="L29">
+        <v>11.9</v>
+      </c>
+      <c r="M29">
+        <v>7.408462500000002</v>
+      </c>
+      <c r="N29">
+        <v>4.491537499999997</v>
+      </c>
+      <c r="O29">
+        <v>1.077968999999999</v>
+      </c>
+      <c r="P29">
+        <v>3.413568499999998</v>
+      </c>
+      <c r="Q29">
+        <v>35.4135685</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1382540838525125</v>
+      </c>
+      <c r="T29">
+        <v>1.505976907849066</v>
+      </c>
+      <c r="U29">
+        <v>0.1125</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>1.606271206744989</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1242911643229954</v>
+      </c>
+      <c r="C30">
+        <v>162.2994350101018</v>
+      </c>
+      <c r="D30">
+        <v>65.59143501010179</v>
+      </c>
+      <c r="E30">
+        <v>-66.00800000000001</v>
+      </c>
+      <c r="F30">
+        <v>68.292</v>
+      </c>
+      <c r="G30">
+        <v>165</v>
+      </c>
+      <c r="H30">
+        <v>109.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>43.9</v>
+      </c>
+      <c r="K30">
+        <v>32</v>
+      </c>
+      <c r="L30">
+        <v>11.9</v>
+      </c>
+      <c r="M30">
+        <v>7.68285</v>
+      </c>
+      <c r="N30">
+        <v>4.217149999999998</v>
+      </c>
+      <c r="O30">
+        <v>1.012116</v>
+      </c>
+      <c r="P30">
+        <v>3.205033999999999</v>
+      </c>
+      <c r="Q30">
+        <v>35.205034</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1393766171152714</v>
+      </c>
+      <c r="T30">
+        <v>1.52297479377313</v>
+      </c>
+      <c r="U30">
+        <v>0.1125</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>1.548904377932668</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1458604686849101</v>
+      </c>
+      <c r="C31">
+        <v>146.6458316868955</v>
+      </c>
+      <c r="D31">
+        <v>52.37683168689549</v>
+      </c>
+      <c r="E31">
+        <v>-63.56900000000002</v>
+      </c>
+      <c r="F31">
+        <v>70.73099999999999</v>
+      </c>
+      <c r="G31">
+        <v>165</v>
+      </c>
+      <c r="H31">
+        <v>109.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>43.9</v>
+      </c>
+      <c r="K31">
+        <v>32</v>
+      </c>
+      <c r="L31">
+        <v>11.9</v>
+      </c>
+      <c r="M31">
+        <v>13.9057146</v>
+      </c>
+      <c r="N31">
+        <v>-2.005714600000001</v>
+      </c>
+      <c r="O31">
+        <v>-0.4813715040000002</v>
+      </c>
+      <c r="P31">
+        <v>-1.524343096000001</v>
+      </c>
+      <c r="Q31">
+        <v>30.475656904</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1416284306789875</v>
+      </c>
+      <c r="T31">
+        <v>1.557072732202354</v>
+      </c>
+      <c r="U31">
+        <v>0.1966</v>
+      </c>
+      <c r="V31">
+        <v>0.2053831882900861</v>
+      </c>
+      <c r="W31">
+        <v>0.1562216651821691</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.8557632845420255</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1474384686849102</v>
+      </c>
+      <c r="C32">
+        <v>143.4460455546679</v>
+      </c>
+      <c r="D32">
+        <v>51.61604555466788</v>
+      </c>
+      <c r="E32">
+        <v>-61.13000000000001</v>
+      </c>
+      <c r="F32">
+        <v>73.17</v>
+      </c>
+      <c r="G32">
+        <v>165</v>
+      </c>
+      <c r="H32">
+        <v>109.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>43.9</v>
+      </c>
+      <c r="K32">
+        <v>32</v>
+      </c>
+      <c r="L32">
+        <v>11.9</v>
+      </c>
+      <c r="M32">
+        <v>14.385222</v>
+      </c>
+      <c r="N32">
+        <v>-2.485222000000002</v>
+      </c>
+      <c r="O32">
+        <v>-0.5964532800000004</v>
+      </c>
+      <c r="P32">
+        <v>-1.888768720000002</v>
+      </c>
+      <c r="Q32">
+        <v>30.11123128</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1430974082601159</v>
+      </c>
+      <c r="T32">
+        <v>1.579316628376673</v>
+      </c>
+      <c r="U32">
+        <v>0.1966</v>
+      </c>
+      <c r="V32">
+        <v>0.1985370820137499</v>
+      </c>
+      <c r="W32">
+        <v>0.1575676096760968</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.827237841723958</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1490164686849101</v>
+      </c>
+      <c r="C33">
+        <v>140.2680441980003</v>
+      </c>
+      <c r="D33">
+        <v>50.87704419800026</v>
+      </c>
+      <c r="E33">
+        <v>-58.69100000000002</v>
+      </c>
+      <c r="F33">
+        <v>75.60899999999999</v>
+      </c>
+      <c r="G33">
+        <v>165</v>
+      </c>
+      <c r="H33">
+        <v>109.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>43.9</v>
+      </c>
+      <c r="K33">
+        <v>32</v>
+      </c>
+      <c r="L33">
+        <v>11.9</v>
+      </c>
+      <c r="M33">
+        <v>14.8647294</v>
+      </c>
+      <c r="N33">
+        <v>-2.9647294</v>
+      </c>
+      <c r="O33">
+        <v>-0.7115350559999999</v>
+      </c>
+      <c r="P33">
+        <v>-2.253194344</v>
+      </c>
+      <c r="Q33">
+        <v>29.746805656</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1446089649015669</v>
+      </c>
+      <c r="T33">
+        <v>1.602205275164741</v>
+      </c>
+      <c r="U33">
+        <v>0.1966</v>
+      </c>
+      <c r="V33">
+        <v>0.1921326600133064</v>
+      </c>
+      <c r="W33">
+        <v>0.158826719041384</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.8005527500554434</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1564704529917823</v>
+      </c>
+      <c r="C34">
+        <v>134.606173210511</v>
+      </c>
+      <c r="D34">
+        <v>47.65417321051098</v>
+      </c>
+      <c r="E34">
+        <v>-56.25200000000001</v>
+      </c>
+      <c r="F34">
+        <v>78.048</v>
+      </c>
+      <c r="G34">
+        <v>165</v>
+      </c>
+      <c r="H34">
+        <v>109.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>43.9</v>
+      </c>
+      <c r="K34">
+        <v>32</v>
+      </c>
+      <c r="L34">
+        <v>11.9</v>
+      </c>
+      <c r="M34">
+        <v>16.6866624</v>
+      </c>
+      <c r="N34">
+        <v>-4.786662400000001</v>
+      </c>
+      <c r="O34">
+        <v>-1.148798976</v>
+      </c>
+      <c r="P34">
+        <v>-3.637863424000001</v>
+      </c>
+      <c r="Q34">
+        <v>28.362136576</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.146712014836696</v>
+      </c>
+      <c r="T34">
+        <v>1.634050570155893</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1711546582257216</v>
+      </c>
+      <c r="W34">
+        <v>0.1772071340713407</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.7131444092738402</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1582204529917823</v>
+      </c>
+      <c r="C35">
+        <v>131.4688438956479</v>
+      </c>
+      <c r="D35">
+        <v>46.95584389564786</v>
+      </c>
+      <c r="E35">
+        <v>-53.813</v>
+      </c>
+      <c r="F35">
+        <v>80.48700000000001</v>
+      </c>
+      <c r="G35">
+        <v>165</v>
+      </c>
+      <c r="H35">
+        <v>109.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>43.9</v>
+      </c>
+      <c r="K35">
+        <v>32</v>
+      </c>
+      <c r="L35">
+        <v>11.9</v>
+      </c>
+      <c r="M35">
+        <v>17.2081206</v>
+      </c>
+      <c r="N35">
+        <v>-5.308120600000002</v>
+      </c>
+      <c r="O35">
+        <v>-1.273948944</v>
+      </c>
+      <c r="P35">
+        <v>-4.034171656000002</v>
+      </c>
+      <c r="Q35">
+        <v>27.965828344</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1483226419238109</v>
+      </c>
+      <c r="T35">
+        <v>1.658439384635831</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1659681534310028</v>
+      </c>
+      <c r="W35">
+        <v>0.1783160087964516</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.6915339726291783</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1599704529917823</v>
+      </c>
+      <c r="C36">
+        <v>128.3516857738576</v>
+      </c>
+      <c r="D36">
+        <v>46.27768577385759</v>
+      </c>
+      <c r="E36">
+        <v>-51.37400000000001</v>
+      </c>
+      <c r="F36">
+        <v>82.926</v>
+      </c>
+      <c r="G36">
+        <v>165</v>
+      </c>
+      <c r="H36">
+        <v>109.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>43.9</v>
+      </c>
+      <c r="K36">
+        <v>32</v>
+      </c>
+      <c r="L36">
+        <v>11.9</v>
+      </c>
+      <c r="M36">
+        <v>17.7295788</v>
+      </c>
+      <c r="N36">
+        <v>-5.8295788</v>
+      </c>
+      <c r="O36">
+        <v>-1.399098912</v>
+      </c>
+      <c r="P36">
+        <v>-4.430479888000001</v>
+      </c>
+      <c r="Q36">
+        <v>27.569520112</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1499820758923535</v>
+      </c>
+      <c r="T36">
+        <v>1.68356725410001</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1610867371536203</v>
+      </c>
+      <c r="W36">
+        <v>0.179359655596556</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6711947381400849</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1617204529917823</v>
+      </c>
+      <c r="C37">
+        <v>125.2538373224151</v>
+      </c>
+      <c r="D37">
+        <v>45.61883732241508</v>
+      </c>
+      <c r="E37">
+        <v>-48.935</v>
+      </c>
+      <c r="F37">
+        <v>85.36500000000001</v>
+      </c>
+      <c r="G37">
+        <v>165</v>
+      </c>
+      <c r="H37">
+        <v>109.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>43.9</v>
+      </c>
+      <c r="K37">
+        <v>32</v>
+      </c>
+      <c r="L37">
+        <v>11.9</v>
+      </c>
+      <c r="M37">
+        <v>18.251037</v>
+      </c>
+      <c r="N37">
+        <v>-6.351037000000002</v>
+      </c>
+      <c r="O37">
+        <v>-1.52424888</v>
+      </c>
+      <c r="P37">
+        <v>-4.826788120000002</v>
+      </c>
+      <c r="Q37">
+        <v>27.17321188</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1516925693676204</v>
+      </c>
+      <c r="T37">
+        <v>1.709468288778472</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1564842589492312</v>
+      </c>
+      <c r="W37">
+        <v>0.1803436654366544</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6520177456217966</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1634704529917823</v>
+      </c>
+      <c r="C38">
+        <v>122.1744853913966</v>
+      </c>
+      <c r="D38">
+        <v>44.97848539139666</v>
+      </c>
+      <c r="E38">
+        <v>-46.49600000000001</v>
+      </c>
+      <c r="F38">
+        <v>87.804</v>
+      </c>
+      <c r="G38">
+        <v>165</v>
+      </c>
+      <c r="H38">
+        <v>109.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>43.9</v>
+      </c>
+      <c r="K38">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>11.9</v>
+      </c>
+      <c r="M38">
+        <v>18.7724952</v>
+      </c>
+      <c r="N38">
+        <v>-6.872495199999999</v>
+      </c>
+      <c r="O38">
+        <v>-1.649398848</v>
+      </c>
+      <c r="P38">
+        <v>-5.223096352</v>
+      </c>
+      <c r="Q38">
+        <v>26.776903648</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1534565157639895</v>
+      </c>
+      <c r="T38">
+        <v>1.736178730790636</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1521374739784192</v>
+      </c>
+      <c r="W38">
+        <v>0.181273008063414</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.6339061415767469</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1652204529917823</v>
+      </c>
+      <c r="C39">
+        <v>119.1128618556302</v>
+      </c>
+      <c r="D39">
+        <v>44.35586185563017</v>
+      </c>
+      <c r="E39">
+        <v>-44.05700000000002</v>
+      </c>
+      <c r="F39">
+        <v>90.24299999999999</v>
+      </c>
+      <c r="G39">
+        <v>165</v>
+      </c>
+      <c r="H39">
+        <v>109.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>43.9</v>
+      </c>
+      <c r="K39">
+        <v>32</v>
+      </c>
+      <c r="L39">
+        <v>11.9</v>
+      </c>
+      <c r="M39">
+        <v>19.2939534</v>
+      </c>
+      <c r="N39">
+        <v>-7.393953400000001</v>
+      </c>
+      <c r="O39">
+        <v>-1.774548816</v>
+      </c>
+      <c r="P39">
+        <v>-5.619404584000001</v>
+      </c>
+      <c r="Q39">
+        <v>26.380595416</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.155276460458656</v>
+      </c>
+      <c r="T39">
+        <v>1.763737123342868</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1480256503573809</v>
+      </c>
+      <c r="W39">
+        <v>0.182152115953592</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6167735431557536</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1669704529917823</v>
+      </c>
+      <c r="C40">
+        <v>116.0682405409241</v>
+      </c>
+      <c r="D40">
+        <v>43.75024054092412</v>
+      </c>
+      <c r="E40">
+        <v>-41.61800000000001</v>
+      </c>
+      <c r="F40">
+        <v>92.682</v>
+      </c>
+      <c r="G40">
+        <v>165</v>
+      </c>
+      <c r="H40">
+        <v>109.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>43.9</v>
+      </c>
+      <c r="K40">
+        <v>32</v>
+      </c>
+      <c r="L40">
+        <v>11.9</v>
+      </c>
+      <c r="M40">
+        <v>19.8154116</v>
+      </c>
+      <c r="N40">
+        <v>-7.915411600000002</v>
+      </c>
+      <c r="O40">
+        <v>-1.899698784000001</v>
+      </c>
+      <c r="P40">
+        <v>-6.015712816000002</v>
+      </c>
+      <c r="Q40">
+        <v>25.984287184</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1571551130466989</v>
+      </c>
+      <c r="T40">
+        <v>1.792184496300011</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1441302385058708</v>
+      </c>
+      <c r="W40">
+        <v>0.1829849550074448</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.6005426604411285</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1687204529917823</v>
+      </c>
+      <c r="C41">
+        <v>113.0399343987152</v>
+      </c>
+      <c r="D41">
+        <v>43.16093439871526</v>
+      </c>
+      <c r="E41">
+        <v>-39.179</v>
+      </c>
+      <c r="F41">
+        <v>95.12100000000001</v>
+      </c>
+      <c r="G41">
+        <v>165</v>
+      </c>
+      <c r="H41">
+        <v>109.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>43.9</v>
+      </c>
+      <c r="K41">
+        <v>32</v>
+      </c>
+      <c r="L41">
+        <v>11.9</v>
+      </c>
+      <c r="M41">
+        <v>20.3368698</v>
+      </c>
+      <c r="N41">
+        <v>-8.436869800000004</v>
+      </c>
+      <c r="O41">
+        <v>-2.024848752000001</v>
+      </c>
+      <c r="P41">
+        <v>-6.412021048000003</v>
+      </c>
+      <c r="Q41">
+        <v>25.587978952</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1590953608015628</v>
+      </c>
+      <c r="T41">
+        <v>1.821564570009847</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1404345913646947</v>
+      </c>
+      <c r="W41">
+        <v>0.1837750843662282</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5851441306862277</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1704704529917823</v>
+      </c>
+      <c r="C42">
+        <v>110.0272929060224</v>
+      </c>
+      <c r="D42">
+        <v>42.58729290602239</v>
+      </c>
+      <c r="E42">
+        <v>-36.74000000000001</v>
+      </c>
+      <c r="F42">
+        <v>97.56</v>
+      </c>
+      <c r="G42">
+        <v>165</v>
+      </c>
+      <c r="H42">
+        <v>109.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>43.9</v>
+      </c>
+      <c r="K42">
+        <v>32</v>
+      </c>
+      <c r="L42">
+        <v>11.9</v>
+      </c>
+      <c r="M42">
+        <v>20.858328</v>
+      </c>
+      <c r="N42">
+        <v>-8.958328000000002</v>
+      </c>
+      <c r="O42">
+        <v>-2.14999872</v>
+      </c>
+      <c r="P42">
+        <v>-6.808329280000001</v>
+      </c>
+      <c r="Q42">
+        <v>25.19167072</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1611002834815888</v>
+      </c>
+      <c r="T42">
+        <v>1.851923979510011</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1369237265805773</v>
+      </c>
+      <c r="W42">
+        <v>0.1845257072570726</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5705155274190721</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1722204529917823</v>
+      </c>
+      <c r="C43">
+        <v>107.0296996700203</v>
+      </c>
+      <c r="D43">
+        <v>42.02869967002032</v>
+      </c>
+      <c r="E43">
+        <v>-34.301</v>
+      </c>
+      <c r="F43">
+        <v>99.99900000000001</v>
+      </c>
+      <c r="G43">
+        <v>165</v>
+      </c>
+      <c r="H43">
+        <v>109.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>43.9</v>
+      </c>
+      <c r="K43">
+        <v>32</v>
+      </c>
+      <c r="L43">
+        <v>11.9</v>
+      </c>
+      <c r="M43">
+        <v>21.3797862</v>
+      </c>
+      <c r="N43">
+        <v>-9.479786200000003</v>
+      </c>
+      <c r="O43">
+        <v>-2.275148688000001</v>
+      </c>
+      <c r="P43">
+        <v>-7.204637512000002</v>
+      </c>
+      <c r="Q43">
+        <v>24.795362488</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1631731696422937</v>
+      </c>
+      <c r="T43">
+        <v>1.883312521535605</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1335841234932461</v>
+      </c>
+      <c r="W43">
+        <v>0.185239714397144</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5566005145551922</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1739704529917823</v>
+      </c>
+      <c r="C44">
+        <v>104.0465702186897</v>
+      </c>
+      <c r="D44">
+        <v>41.48457021868967</v>
+      </c>
+      <c r="E44">
+        <v>-31.86200000000001</v>
+      </c>
+      <c r="F44">
+        <v>102.438</v>
+      </c>
+      <c r="G44">
+        <v>165</v>
+      </c>
+      <c r="H44">
+        <v>109.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>43.9</v>
+      </c>
+      <c r="K44">
+        <v>32</v>
+      </c>
+      <c r="L44">
+        <v>11.9</v>
+      </c>
+      <c r="M44">
+        <v>21.9012444</v>
+      </c>
+      <c r="N44">
+        <v>-10.0012444</v>
+      </c>
+      <c r="O44">
+        <v>-2.400298656</v>
+      </c>
+      <c r="P44">
+        <v>-7.600945744000001</v>
+      </c>
+      <c r="Q44">
+        <v>24.399054256</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1653175346361264</v>
+      </c>
+      <c r="T44">
+        <v>1.915783427079322</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1304035491243593</v>
+      </c>
+      <c r="W44">
+        <v>0.185919721197212</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5433481213514972</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1757204529917823</v>
+      </c>
+      <c r="C45">
+        <v>101.0773499608947</v>
+      </c>
+      <c r="D45">
+        <v>40.95434996089471</v>
+      </c>
+      <c r="E45">
+        <v>-29.42300000000002</v>
+      </c>
+      <c r="F45">
+        <v>104.877</v>
+      </c>
+      <c r="G45">
+        <v>165</v>
+      </c>
+      <c r="H45">
+        <v>109.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>43.9</v>
+      </c>
+      <c r="K45">
+        <v>32</v>
+      </c>
+      <c r="L45">
+        <v>11.9</v>
+      </c>
+      <c r="M45">
+        <v>22.4227026</v>
+      </c>
+      <c r="N45">
+        <v>-10.5227026</v>
+      </c>
+      <c r="O45">
+        <v>-2.525448624</v>
+      </c>
+      <c r="P45">
+        <v>-7.997253976</v>
+      </c>
+      <c r="Q45">
+        <v>24.002746024</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1675371405069356</v>
+      </c>
+      <c r="T45">
+        <v>1.949393662642117</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1273709084470487</v>
+      </c>
+      <c r="W45">
+        <v>0.186568099774021</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5307121185293695</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1774704529917823</v>
+      </c>
+      <c r="C46">
+        <v>98.12151230092243</v>
+      </c>
+      <c r="D46">
+        <v>40.43751230092244</v>
+      </c>
+      <c r="E46">
+        <v>-26.98400000000001</v>
+      </c>
+      <c r="F46">
+        <v>107.316</v>
+      </c>
+      <c r="G46">
+        <v>165</v>
+      </c>
+      <c r="H46">
+        <v>109.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>43.9</v>
+      </c>
+      <c r="K46">
+        <v>32</v>
+      </c>
+      <c r="L46">
+        <v>11.9</v>
+      </c>
+      <c r="M46">
+        <v>22.9441608</v>
+      </c>
+      <c r="N46">
+        <v>-11.0441608</v>
+      </c>
+      <c r="O46">
+        <v>-2.650598592</v>
+      </c>
+      <c r="P46">
+        <v>-8.393562208000001</v>
+      </c>
+      <c r="Q46">
+        <v>23.606437792</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.169836018015988</v>
+      </c>
+      <c r="T46">
+        <v>1.984204263760726</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1244761150732521</v>
+      </c>
+      <c r="W46">
+        <v>0.1871870065973387</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5186504794718837</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1792204529917823</v>
+      </c>
+      <c r="C47">
+        <v>95.17855689400777</v>
+      </c>
+      <c r="D47">
+        <v>39.93355689400779</v>
+      </c>
+      <c r="E47">
+        <v>-24.545</v>
+      </c>
+      <c r="F47">
+        <v>109.755</v>
+      </c>
+      <c r="G47">
+        <v>165</v>
+      </c>
+      <c r="H47">
+        <v>109.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>43.9</v>
+      </c>
+      <c r="K47">
+        <v>32</v>
+      </c>
+      <c r="L47">
+        <v>11.9</v>
+      </c>
+      <c r="M47">
+        <v>23.465619</v>
+      </c>
+      <c r="N47">
+        <v>-11.565619</v>
+      </c>
+      <c r="O47">
+        <v>-2.77574856</v>
+      </c>
+      <c r="P47">
+        <v>-8.789870440000001</v>
+      </c>
+      <c r="Q47">
+        <v>23.21012956</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1722184910708242</v>
+      </c>
+      <c r="T47">
+        <v>2.020280704920012</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1217099791827354</v>
+      </c>
+      <c r="W47">
+        <v>0.1877784064507312</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5071249132613973</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1929155814607446</v>
+      </c>
+      <c r="C48">
+        <v>89.1909527444309</v>
+      </c>
+      <c r="D48">
+        <v>36.38495274443092</v>
+      </c>
+      <c r="E48">
+        <v>-22.10600000000001</v>
+      </c>
+      <c r="F48">
+        <v>112.194</v>
+      </c>
+      <c r="G48">
+        <v>165</v>
+      </c>
+      <c r="H48">
+        <v>109.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>43.9</v>
+      </c>
+      <c r="K48">
+        <v>32</v>
+      </c>
+      <c r="L48">
+        <v>11.9</v>
+      </c>
+      <c r="M48">
+        <v>26.7919272</v>
+      </c>
+      <c r="N48">
+        <v>-14.8919272</v>
+      </c>
+      <c r="O48">
+        <v>-3.574062528000001</v>
+      </c>
+      <c r="P48">
+        <v>-11.317864672</v>
+      </c>
+      <c r="Q48">
+        <v>20.68213532799999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1755135158479917</v>
+      </c>
+      <c r="T48">
+        <v>2.070175400371268</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1065992744262159</v>
+      </c>
+      <c r="W48">
+        <v>0.2133440932670196</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4441636434425664</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1949155814607446</v>
+      </c>
+      <c r="C49">
+        <v>86.28582434899485</v>
+      </c>
+      <c r="D49">
+        <v>35.91882434899487</v>
+      </c>
+      <c r="E49">
+        <v>-19.667</v>
+      </c>
+      <c r="F49">
+        <v>114.633</v>
+      </c>
+      <c r="G49">
+        <v>165</v>
+      </c>
+      <c r="H49">
+        <v>109.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>43.9</v>
+      </c>
+      <c r="K49">
+        <v>32</v>
+      </c>
+      <c r="L49">
+        <v>11.9</v>
+      </c>
+      <c r="M49">
+        <v>27.3743604</v>
+      </c>
+      <c r="N49">
+        <v>-15.47436040000001</v>
+      </c>
+      <c r="O49">
+        <v>-3.713846496000001</v>
+      </c>
+      <c r="P49">
+        <v>-11.760513904</v>
+      </c>
+      <c r="Q49">
+        <v>20.239486096</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1780930161470104</v>
+      </c>
+      <c r="T49">
+        <v>2.109235313585821</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.104331204757573</v>
+      </c>
+      <c r="W49">
+        <v>0.2138857083038916</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4347133531565543</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1969155814607446</v>
+      </c>
+      <c r="C50">
+        <v>83.39248804618194</v>
+      </c>
+      <c r="D50">
+        <v>35.46448804618196</v>
+      </c>
+      <c r="E50">
+        <v>-17.22800000000001</v>
+      </c>
+      <c r="F50">
+        <v>117.072</v>
+      </c>
+      <c r="G50">
+        <v>165</v>
+      </c>
+      <c r="H50">
+        <v>109.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>43.9</v>
+      </c>
+      <c r="K50">
+        <v>32</v>
+      </c>
+      <c r="L50">
+        <v>11.9</v>
+      </c>
+      <c r="M50">
+        <v>27.9567936</v>
+      </c>
+      <c r="N50">
+        <v>-16.0567936</v>
+      </c>
+      <c r="O50">
+        <v>-3.853630464000001</v>
+      </c>
+      <c r="P50">
+        <v>-12.203163136</v>
+      </c>
+      <c r="Q50">
+        <v>19.796836864</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1807717279959914</v>
+      </c>
+      <c r="T50">
+        <v>2.149797531154779</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1021576379917903</v>
+      </c>
+      <c r="W50">
+        <v>0.2144047560475605</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4256568249657928</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1989155814607446</v>
+      </c>
+      <c r="C51">
+        <v>80.51050195172897</v>
+      </c>
+      <c r="D51">
+        <v>35.02150195172896</v>
+      </c>
+      <c r="E51">
+        <v>-14.78900000000002</v>
+      </c>
+      <c r="F51">
+        <v>119.511</v>
+      </c>
+      <c r="G51">
+        <v>165</v>
+      </c>
+      <c r="H51">
+        <v>109.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>43.9</v>
+      </c>
+      <c r="K51">
+        <v>32</v>
+      </c>
+      <c r="L51">
+        <v>11.9</v>
+      </c>
+      <c r="M51">
+        <v>28.5392268</v>
+      </c>
+      <c r="N51">
+        <v>-16.6392268</v>
+      </c>
+      <c r="O51">
+        <v>-3.993414432000001</v>
+      </c>
+      <c r="P51">
+        <v>-12.645812368</v>
+      </c>
+      <c r="Q51">
+        <v>19.354187632</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1835554873684618</v>
+      </c>
+      <c r="T51">
+        <v>2.19195042392252</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1000727882368558</v>
+      </c>
+      <c r="W51">
+        <v>0.2149026181690388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4169699509868992</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2009155814607446</v>
+      </c>
+      <c r="C52">
+        <v>77.63944598726009</v>
+      </c>
+      <c r="D52">
+        <v>34.58944598726008</v>
+      </c>
+      <c r="E52">
+        <v>-12.35000000000001</v>
+      </c>
+      <c r="F52">
+        <v>121.95</v>
+      </c>
+      <c r="G52">
+        <v>165</v>
+      </c>
+      <c r="H52">
+        <v>109.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>43.9</v>
+      </c>
+      <c r="K52">
+        <v>32</v>
+      </c>
+      <c r="L52">
+        <v>11.9</v>
+      </c>
+      <c r="M52">
+        <v>29.12166</v>
+      </c>
+      <c r="N52">
+        <v>-17.22166</v>
+      </c>
+      <c r="O52">
+        <v>-4.1331984</v>
+      </c>
+      <c r="P52">
+        <v>-13.0884616</v>
+      </c>
+      <c r="Q52">
+        <v>18.9115384</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.186450597115831</v>
+      </c>
+      <c r="T52">
+        <v>2.23578943240097</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.09807133247211867</v>
+      </c>
+      <c r="W52">
+        <v>0.2153805658056581</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4086305519671611</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2029155814607446</v>
+      </c>
+      <c r="C53">
+        <v>74.77892055159589</v>
+      </c>
+      <c r="D53">
+        <v>34.1679205515959</v>
+      </c>
+      <c r="E53">
+        <v>-9.911000000000001</v>
+      </c>
+      <c r="F53">
+        <v>124.389</v>
+      </c>
+      <c r="G53">
+        <v>165</v>
+      </c>
+      <c r="H53">
+        <v>109.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>43.9</v>
+      </c>
+      <c r="K53">
+        <v>32</v>
+      </c>
+      <c r="L53">
+        <v>11.9</v>
+      </c>
+      <c r="M53">
+        <v>29.7040932</v>
+      </c>
+      <c r="N53">
+        <v>-17.8040932</v>
+      </c>
+      <c r="O53">
+        <v>-4.272982368000001</v>
+      </c>
+      <c r="P53">
+        <v>-13.531110832</v>
+      </c>
+      <c r="Q53">
+        <v>18.468889168</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1894638746079909</v>
+      </c>
+      <c r="T53">
+        <v>2.281417788164255</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.09614836516874378</v>
+      </c>
+      <c r="W53">
+        <v>0.215839770397704</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.4006181882030991</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2049155814607446</v>
+      </c>
+      <c r="C54">
+        <v>71.9285452880458</v>
+      </c>
+      <c r="D54">
+        <v>33.7565452880458</v>
+      </c>
+      <c r="E54">
+        <v>-7.472000000000008</v>
+      </c>
+      <c r="F54">
+        <v>126.828</v>
+      </c>
+      <c r="G54">
+        <v>165</v>
+      </c>
+      <c r="H54">
+        <v>109.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>43.9</v>
+      </c>
+      <c r="K54">
+        <v>32</v>
+      </c>
+      <c r="L54">
+        <v>11.9</v>
+      </c>
+      <c r="M54">
+        <v>30.2865264</v>
+      </c>
+      <c r="N54">
+        <v>-18.3865264</v>
+      </c>
+      <c r="O54">
+        <v>-4.412766336000001</v>
+      </c>
+      <c r="P54">
+        <v>-13.973760064</v>
+      </c>
+      <c r="Q54">
+        <v>18.026239936</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1926027053289907</v>
+      </c>
+      <c r="T54">
+        <v>2.328947325417678</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.09429935814626794</v>
+      </c>
+      <c r="W54">
+        <v>0.2162813132746712</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3929139922761165</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2069155814607445</v>
+      </c>
+      <c r="C55">
+        <v>69.08795793969014</v>
+      </c>
+      <c r="D55">
+        <v>33.35495793969014</v>
+      </c>
+      <c r="E55">
+        <v>-5.033000000000015</v>
+      </c>
+      <c r="F55">
+        <v>129.267</v>
+      </c>
+      <c r="G55">
+        <v>165</v>
+      </c>
+      <c r="H55">
+        <v>109.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>43.9</v>
+      </c>
+      <c r="K55">
+        <v>32</v>
+      </c>
+      <c r="L55">
+        <v>11.9</v>
+      </c>
+      <c r="M55">
+        <v>30.8689596</v>
+      </c>
+      <c r="N55">
+        <v>-18.9689596</v>
+      </c>
+      <c r="O55">
+        <v>-4.552550304</v>
+      </c>
+      <c r="P55">
+        <v>-14.416409296</v>
+      </c>
+      <c r="Q55">
+        <v>17.583590704</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1958751033147139</v>
+      </c>
+      <c r="T55">
+        <v>2.378499396171245</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.09252012497369687</v>
+      </c>
+      <c r="W55">
+        <v>0.2167061941562812</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.385500520723737</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2089155814607446</v>
+      </c>
+      <c r="C56">
+        <v>66.2568132854112</v>
+      </c>
+      <c r="D56">
+        <v>32.96281328541122</v>
+      </c>
+      <c r="E56">
+        <v>-2.593999999999994</v>
+      </c>
+      <c r="F56">
+        <v>131.706</v>
+      </c>
+      <c r="G56">
+        <v>165</v>
+      </c>
+      <c r="H56">
+        <v>109.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>43.9</v>
+      </c>
+      <c r="K56">
+        <v>32</v>
+      </c>
+      <c r="L56">
+        <v>11.9</v>
+      </c>
+      <c r="M56">
+        <v>31.4513928</v>
+      </c>
+      <c r="N56">
+        <v>-19.55139280000001</v>
+      </c>
+      <c r="O56">
+        <v>-4.692334272000001</v>
+      </c>
+      <c r="P56">
+        <v>-14.85905852800001</v>
+      </c>
+      <c r="Q56">
+        <v>17.14094147199999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1992897794737294</v>
+      </c>
+      <c r="T56">
+        <v>2.430205904783663</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.09080678932603579</v>
+      </c>
+      <c r="W56">
+        <v>0.2171153387089427</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3783616221918158</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2109155814607446</v>
+      </c>
+      <c r="C57">
+        <v>63.43478215010484</v>
+      </c>
+      <c r="D57">
+        <v>32.57978215010485</v>
+      </c>
+      <c r="E57">
+        <v>-0.1550000000000011</v>
+      </c>
+      <c r="F57">
+        <v>134.145</v>
+      </c>
+      <c r="G57">
+        <v>165</v>
+      </c>
+      <c r="H57">
+        <v>109.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>43.9</v>
+      </c>
+      <c r="K57">
+        <v>32</v>
+      </c>
+      <c r="L57">
+        <v>11.9</v>
+      </c>
+      <c r="M57">
+        <v>32.033826</v>
+      </c>
+      <c r="N57">
+        <v>-20.13382600000001</v>
+      </c>
+      <c r="O57">
+        <v>-4.832118240000002</v>
+      </c>
+      <c r="P57">
+        <v>-15.30170776</v>
+      </c>
+      <c r="Q57">
+        <v>16.69829223999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2028562190175901</v>
+      </c>
+      <c r="T57">
+        <v>2.484210480445523</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.08915575679283515</v>
+      </c>
+      <c r="W57">
+        <v>0.217509605277871</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3714823199701465</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2129155814607446</v>
+      </c>
+      <c r="C58">
+        <v>60.62155048310782</v>
+      </c>
+      <c r="D58">
+        <v>32.20555048310784</v>
+      </c>
+      <c r="E58">
+        <v>2.283999999999992</v>
+      </c>
+      <c r="F58">
+        <v>136.584</v>
+      </c>
+      <c r="G58">
+        <v>165</v>
+      </c>
+      <c r="H58">
+        <v>109.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>43.9</v>
+      </c>
+      <c r="K58">
+        <v>32</v>
+      </c>
+      <c r="L58">
+        <v>11.9</v>
+      </c>
+      <c r="M58">
+        <v>32.6162592</v>
+      </c>
+      <c r="N58">
+        <v>-20.7162592</v>
+      </c>
+      <c r="O58">
+        <v>-4.971902208</v>
+      </c>
+      <c r="P58">
+        <v>-15.744356992</v>
+      </c>
+      <c r="Q58">
+        <v>16.255643008</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.206584769449808</v>
+      </c>
+      <c r="T58">
+        <v>2.540669809546557</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.08756368970724882</v>
+      </c>
+      <c r="W58">
+        <v>0.217889790897909</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3648487071135368</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2149155814607446</v>
+      </c>
+      <c r="C59">
+        <v>57.81681849941862</v>
+      </c>
+      <c r="D59">
+        <v>31.83981849941864</v>
+      </c>
+      <c r="E59">
+        <v>4.723000000000013</v>
+      </c>
+      <c r="F59">
+        <v>139.023</v>
+      </c>
+      <c r="G59">
+        <v>165</v>
+      </c>
+      <c r="H59">
+        <v>109.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>43.9</v>
+      </c>
+      <c r="K59">
+        <v>32</v>
+      </c>
+      <c r="L59">
+        <v>11.9</v>
+      </c>
+      <c r="M59">
+        <v>33.19869240000001</v>
+      </c>
+      <c r="N59">
+        <v>-21.29869240000001</v>
+      </c>
+      <c r="O59">
+        <v>-5.111686176000002</v>
+      </c>
+      <c r="P59">
+        <v>-16.187006224</v>
+      </c>
+      <c r="Q59">
+        <v>15.812993776</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2104867408323617</v>
+      </c>
+      <c r="T59">
+        <v>2.599755153954617</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.08602748462466549</v>
+      </c>
+      <c r="W59">
+        <v>0.2182566366716299</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3584478526027729</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2169155814607446</v>
+      </c>
+      <c r="C60">
+        <v>55.02029987877583</v>
+      </c>
+      <c r="D60">
+        <v>31.48229987877583</v>
+      </c>
+      <c r="E60">
+        <v>7.161999999999978</v>
+      </c>
+      <c r="F60">
+        <v>141.462</v>
+      </c>
+      <c r="G60">
+        <v>165</v>
+      </c>
+      <c r="H60">
+        <v>109.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>43.9</v>
+      </c>
+      <c r="K60">
+        <v>32</v>
+      </c>
+      <c r="L60">
+        <v>11.9</v>
+      </c>
+      <c r="M60">
+        <v>33.7811256</v>
+      </c>
+      <c r="N60">
+        <v>-21.8811256</v>
+      </c>
+      <c r="O60">
+        <v>-5.251470143999999</v>
+      </c>
+      <c r="P60">
+        <v>-16.629655456</v>
+      </c>
+      <c r="Q60">
+        <v>15.370344544</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2145745203759893</v>
+      </c>
+      <c r="T60">
+        <v>2.661654086191631</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.0845442521311368</v>
+      </c>
+      <c r="W60">
+        <v>0.2186108325910845</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.35226771721307</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2189155814607446</v>
+      </c>
+      <c r="C61">
+        <v>52.23172101809703</v>
+      </c>
+      <c r="D61">
+        <v>31.132721018097</v>
+      </c>
+      <c r="E61">
+        <v>9.600999999999971</v>
+      </c>
+      <c r="F61">
+        <v>143.901</v>
+      </c>
+      <c r="G61">
+        <v>165</v>
+      </c>
+      <c r="H61">
+        <v>109.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>43.9</v>
+      </c>
+      <c r="K61">
+        <v>32</v>
+      </c>
+      <c r="L61">
+        <v>11.9</v>
+      </c>
+      <c r="M61">
+        <v>34.3635588</v>
+      </c>
+      <c r="N61">
+        <v>-22.4635588</v>
+      </c>
+      <c r="O61">
+        <v>-5.391254112</v>
+      </c>
+      <c r="P61">
+        <v>-17.072304688</v>
+      </c>
+      <c r="Q61">
+        <v>14.927695312</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2188617037997939</v>
+      </c>
+      <c r="T61">
+        <v>2.726572478537768</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08311129870518533</v>
+      </c>
+      <c r="W61">
+        <v>0.2189530218692018</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3462970779382721</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2209155814607445</v>
+      </c>
+      <c r="C62">
+        <v>49.45082033317613</v>
+      </c>
+      <c r="D62">
+        <v>30.79082033317612</v>
+      </c>
+      <c r="E62">
+        <v>12.03999999999999</v>
+      </c>
+      <c r="F62">
+        <v>146.34</v>
+      </c>
+      <c r="G62">
+        <v>165</v>
+      </c>
+      <c r="H62">
+        <v>109.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>43.9</v>
+      </c>
+      <c r="K62">
+        <v>32</v>
+      </c>
+      <c r="L62">
+        <v>11.9</v>
+      </c>
+      <c r="M62">
+        <v>34.945992</v>
+      </c>
+      <c r="N62">
+        <v>-23.04599200000001</v>
+      </c>
+      <c r="O62">
+        <v>-5.531038080000001</v>
+      </c>
+      <c r="P62">
+        <v>-17.51495392</v>
+      </c>
+      <c r="Q62">
+        <v>14.48504608</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2233632463947888</v>
+      </c>
+      <c r="T62">
+        <v>2.794736790501213</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.08172611039343222</v>
+      </c>
+      <c r="W62">
+        <v>0.2192838048380484</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3405254599726343</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2229155814607446</v>
+      </c>
+      <c r="C63">
+        <v>46.67734760589377</v>
+      </c>
+      <c r="D63">
+        <v>30.45634760589376</v>
+      </c>
+      <c r="E63">
+        <v>14.47899999999998</v>
+      </c>
+      <c r="F63">
+        <v>148.779</v>
+      </c>
+      <c r="G63">
+        <v>165</v>
+      </c>
+      <c r="H63">
+        <v>109.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>43.9</v>
+      </c>
+      <c r="K63">
+        <v>32</v>
+      </c>
+      <c r="L63">
+        <v>11.9</v>
+      </c>
+      <c r="M63">
+        <v>35.5284252</v>
+      </c>
+      <c r="N63">
+        <v>-23.6284252</v>
+      </c>
+      <c r="O63">
+        <v>-5.670822048000001</v>
+      </c>
+      <c r="P63">
+        <v>-17.957603152</v>
+      </c>
+      <c r="Q63">
+        <v>14.042396848</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2280956373279885</v>
+      </c>
+      <c r="T63">
+        <v>2.866396708206372</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08038633809190054</v>
+      </c>
+      <c r="W63">
+        <v>0.2196037424636542</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.334943075382919</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2249155814607446</v>
+      </c>
+      <c r="C64">
+        <v>43.91106337351673</v>
+      </c>
+      <c r="D64">
+        <v>30.12906337351671</v>
+      </c>
+      <c r="E64">
+        <v>16.91799999999998</v>
+      </c>
+      <c r="F64">
+        <v>151.218</v>
+      </c>
+      <c r="G64">
+        <v>165</v>
+      </c>
+      <c r="H64">
+        <v>109.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>43.9</v>
+      </c>
+      <c r="K64">
+        <v>32</v>
+      </c>
+      <c r="L64">
+        <v>11.9</v>
+      </c>
+      <c r="M64">
+        <v>36.1108584</v>
+      </c>
+      <c r="N64">
+        <v>-24.2108584</v>
+      </c>
+      <c r="O64">
+        <v>-5.810606015999999</v>
+      </c>
+      <c r="P64">
+        <v>-18.400252384</v>
+      </c>
+      <c r="Q64">
+        <v>13.599747616</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2330771014681987</v>
+      </c>
+      <c r="T64">
+        <v>2.941828200527592</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.07908978425170862</v>
+      </c>
+      <c r="W64">
+        <v>0.219913359520692</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3295407677154526</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2269155814607446</v>
+      </c>
+      <c r="C65">
+        <v>41.15173835695444</v>
+      </c>
+      <c r="D65">
+        <v>29.80873835695444</v>
+      </c>
+      <c r="E65">
+        <v>19.357</v>
+      </c>
+      <c r="F65">
+        <v>153.657</v>
+      </c>
+      <c r="G65">
+        <v>165</v>
+      </c>
+      <c r="H65">
+        <v>109.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>43.9</v>
+      </c>
+      <c r="K65">
+        <v>32</v>
+      </c>
+      <c r="L65">
+        <v>11.9</v>
+      </c>
+      <c r="M65">
+        <v>36.6932916</v>
+      </c>
+      <c r="N65">
+        <v>-24.7932916</v>
+      </c>
+      <c r="O65">
+        <v>-5.950389984000001</v>
+      </c>
+      <c r="P65">
+        <v>-18.842901616</v>
+      </c>
+      <c r="Q65">
+        <v>13.157098384</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2383278339403122</v>
+      </c>
+      <c r="T65">
+        <v>3.021337070812122</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.07783439085088784</v>
+      </c>
+      <c r="W65">
+        <v>0.220213147464808</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3243099618786993</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2289155814607446</v>
+      </c>
+      <c r="C66">
+        <v>38.39915292510378</v>
+      </c>
+      <c r="D66">
+        <v>29.49515292510378</v>
+      </c>
+      <c r="E66">
+        <v>21.79599999999999</v>
+      </c>
+      <c r="F66">
+        <v>156.096</v>
+      </c>
+      <c r="G66">
+        <v>165</v>
+      </c>
+      <c r="H66">
+        <v>109.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>43.9</v>
+      </c>
+      <c r="K66">
+        <v>32</v>
+      </c>
+      <c r="L66">
+        <v>11.9</v>
+      </c>
+      <c r="M66">
+        <v>37.27572480000001</v>
+      </c>
+      <c r="N66">
+        <v>-25.37572480000001</v>
+      </c>
+      <c r="O66">
+        <v>-6.090173952000002</v>
+      </c>
+      <c r="P66">
+        <v>-19.28555084800001</v>
+      </c>
+      <c r="Q66">
+        <v>12.71444915199999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2438702737719876</v>
+      </c>
+      <c r="T66">
+        <v>3.105263100556903</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.0766182284938427</v>
+      </c>
+      <c r="W66">
+        <v>0.2205035670356704</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3192426187243446</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2309155814607445</v>
+      </c>
+      <c r="C67">
+        <v>35.65309659265185</v>
+      </c>
+      <c r="D67">
+        <v>29.18809659265184</v>
+      </c>
+      <c r="E67">
+        <v>24.23499999999999</v>
+      </c>
+      <c r="F67">
+        <v>158.535</v>
+      </c>
+      <c r="G67">
+        <v>165</v>
+      </c>
+      <c r="H67">
+        <v>109.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>43.9</v>
+      </c>
+      <c r="K67">
+        <v>32</v>
+      </c>
+      <c r="L67">
+        <v>11.9</v>
+      </c>
+      <c r="M67">
+        <v>37.858158</v>
+      </c>
+      <c r="N67">
+        <v>-25.958158</v>
+      </c>
+      <c r="O67">
+        <v>-6.229957920000001</v>
+      </c>
+      <c r="P67">
+        <v>-19.72820008</v>
+      </c>
+      <c r="Q67">
+        <v>12.27179992</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2497294244511872</v>
+      </c>
+      <c r="T67">
+        <v>3.193984903429957</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07543948651701436</v>
+      </c>
+      <c r="W67">
+        <v>0.220785050619737</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3143311938208931</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2329155814607446</v>
+      </c>
+      <c r="C68">
+        <v>32.9133675489243</v>
+      </c>
+      <c r="D68">
+        <v>28.88736754892431</v>
+      </c>
+      <c r="E68">
+        <v>26.67400000000001</v>
+      </c>
+      <c r="F68">
+        <v>160.974</v>
+      </c>
+      <c r="G68">
+        <v>165</v>
+      </c>
+      <c r="H68">
+        <v>109.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>43.9</v>
+      </c>
+      <c r="K68">
+        <v>32</v>
+      </c>
+      <c r="L68">
+        <v>11.9</v>
+      </c>
+      <c r="M68">
+        <v>38.44059120000001</v>
+      </c>
+      <c r="N68">
+        <v>-26.54059120000001</v>
+      </c>
+      <c r="O68">
+        <v>-6.369741888000002</v>
+      </c>
+      <c r="P68">
+        <v>-20.17084931200001</v>
+      </c>
+      <c r="Q68">
+        <v>11.82915068799999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2559332310526927</v>
+      </c>
+      <c r="T68">
+        <v>3.28792563588378</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07429646399402928</v>
+      </c>
+      <c r="W68">
+        <v>0.2210580043982258</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.309568599975122</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2349155814607446</v>
+      </c>
+      <c r="C69">
+        <v>30.17977221556262</v>
+      </c>
+      <c r="D69">
+        <v>28.59277221556262</v>
+      </c>
+      <c r="E69">
+        <v>29.113</v>
+      </c>
+      <c r="F69">
+        <v>163.413</v>
+      </c>
+      <c r="G69">
+        <v>165</v>
+      </c>
+      <c r="H69">
+        <v>109.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>43.9</v>
+      </c>
+      <c r="K69">
+        <v>32</v>
+      </c>
+      <c r="L69">
+        <v>11.9</v>
+      </c>
+      <c r="M69">
+        <v>39.0230244</v>
+      </c>
+      <c r="N69">
+        <v>-27.12302440000001</v>
+      </c>
+      <c r="O69">
+        <v>-6.509525856000001</v>
+      </c>
+      <c r="P69">
+        <v>-20.61349854400001</v>
+      </c>
+      <c r="Q69">
+        <v>11.38650145599999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2625130259330773</v>
+      </c>
+      <c r="T69">
+        <v>3.387559746062077</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07318756154635722</v>
+      </c>
+      <c r="W69">
+        <v>0.2213228103027299</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3049481731098217</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2369155814607446</v>
+      </c>
+      <c r="C70">
+        <v>27.45212483099303</v>
+      </c>
+      <c r="D70">
+        <v>28.30412483099305</v>
+      </c>
+      <c r="E70">
+        <v>31.55199999999999</v>
+      </c>
+      <c r="F70">
+        <v>165.852</v>
+      </c>
+      <c r="G70">
+        <v>165</v>
+      </c>
+      <c r="H70">
+        <v>109.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>43.9</v>
+      </c>
+      <c r="K70">
+        <v>32</v>
+      </c>
+      <c r="L70">
+        <v>11.9</v>
+      </c>
+      <c r="M70">
+        <v>39.6054576</v>
+      </c>
+      <c r="N70">
+        <v>-27.7054576</v>
+      </c>
+      <c r="O70">
+        <v>-6.649309824</v>
+      </c>
+      <c r="P70">
+        <v>-21.056147776</v>
+      </c>
+      <c r="Q70">
+        <v>10.943852224</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.269504057993486</v>
+      </c>
+      <c r="T70">
+        <v>3.493420988126517</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07211127387655784</v>
+      </c>
+      <c r="W70">
+        <v>0.221579827798278</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3004636411523244</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2389155814607446</v>
+      </c>
+      <c r="C71">
+        <v>24.73024705981311</v>
+      </c>
+      <c r="D71">
+        <v>28.02124705981314</v>
+      </c>
+      <c r="E71">
+        <v>33.99100000000001</v>
+      </c>
+      <c r="F71">
+        <v>168.291</v>
+      </c>
+      <c r="G71">
+        <v>165</v>
+      </c>
+      <c r="H71">
+        <v>109.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>43.9</v>
+      </c>
+      <c r="K71">
+        <v>32</v>
+      </c>
+      <c r="L71">
+        <v>11.9</v>
+      </c>
+      <c r="M71">
+        <v>40.18789080000001</v>
+      </c>
+      <c r="N71">
+        <v>-28.28789080000001</v>
+      </c>
+      <c r="O71">
+        <v>-6.789093792000001</v>
+      </c>
+      <c r="P71">
+        <v>-21.498797008</v>
+      </c>
+      <c r="Q71">
+        <v>10.501202992</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2769461243803727</v>
+      </c>
+      <c r="T71">
+        <v>3.606111987743501</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07106618295081063</v>
+      </c>
+      <c r="W71">
+        <v>0.2218293955113464</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2961090956283776</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2409155814607446</v>
+      </c>
+      <c r="C72">
+        <v>22.01396762536976</v>
+      </c>
+      <c r="D72">
+        <v>27.74396762536978</v>
+      </c>
+      <c r="E72">
+        <v>36.43000000000001</v>
+      </c>
+      <c r="F72">
+        <v>170.73</v>
+      </c>
+      <c r="G72">
+        <v>165</v>
+      </c>
+      <c r="H72">
+        <v>109.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>43.9</v>
+      </c>
+      <c r="K72">
+        <v>32</v>
+      </c>
+      <c r="L72">
+        <v>11.9</v>
+      </c>
+      <c r="M72">
+        <v>40.77032400000001</v>
+      </c>
+      <c r="N72">
+        <v>-28.87032400000001</v>
+      </c>
+      <c r="O72">
+        <v>-6.928877760000002</v>
+      </c>
+      <c r="P72">
+        <v>-21.94144624000001</v>
+      </c>
+      <c r="Q72">
+        <v>10.05855375999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2848843285263851</v>
+      </c>
+      <c r="T72">
+        <v>3.726315720668285</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07005095176579904</v>
+      </c>
+      <c r="W72">
+        <v>0.2220718327183272</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2918789656908294</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2429155814607445</v>
+      </c>
+      <c r="C73">
+        <v>19.30312196393794</v>
+      </c>
+      <c r="D73">
+        <v>27.47212196393793</v>
+      </c>
+      <c r="E73">
+        <v>38.86899999999997</v>
+      </c>
+      <c r="F73">
+        <v>173.169</v>
+      </c>
+      <c r="G73">
+        <v>165</v>
+      </c>
+      <c r="H73">
+        <v>109.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>43.9</v>
+      </c>
+      <c r="K73">
+        <v>32</v>
+      </c>
+      <c r="L73">
+        <v>11.9</v>
+      </c>
+      <c r="M73">
+        <v>41.3527572</v>
+      </c>
+      <c r="N73">
+        <v>-29.4527572</v>
+      </c>
+      <c r="O73">
+        <v>-7.068661727999999</v>
+      </c>
+      <c r="P73">
+        <v>-22.384095472</v>
+      </c>
+      <c r="Q73">
+        <v>9.615904527999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2933699950272949</v>
+      </c>
+      <c r="T73">
+        <v>3.854809366208569</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.0690643186423371</v>
+      </c>
+      <c r="W73">
+        <v>0.2223074407082099</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2877679943430712</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2449155814607445</v>
+      </c>
+      <c r="C74">
+        <v>16.59755189903316</v>
+      </c>
+      <c r="D74">
+        <v>27.20555189903316</v>
+      </c>
+      <c r="E74">
+        <v>41.30799999999999</v>
+      </c>
+      <c r="F74">
+        <v>175.608</v>
+      </c>
+      <c r="G74">
+        <v>165</v>
+      </c>
+      <c r="H74">
+        <v>109.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>43.9</v>
+      </c>
+      <c r="K74">
+        <v>32</v>
+      </c>
+      <c r="L74">
+        <v>11.9</v>
+      </c>
+      <c r="M74">
+        <v>41.9351904</v>
+      </c>
+      <c r="N74">
+        <v>-30.0351904</v>
+      </c>
+      <c r="O74">
+        <v>-7.208445696000001</v>
+      </c>
+      <c r="P74">
+        <v>-22.826744704</v>
+      </c>
+      <c r="Q74">
+        <v>9.173255295999997</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.302461780563984</v>
+      </c>
+      <c r="T74">
+        <v>3.992481129287447</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.06810509199452686</v>
+      </c>
+      <c r="W74">
+        <v>0.222536504031707</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2837712166438618</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2469155814607445</v>
+      </c>
+      <c r="C75">
+        <v>13.89710533450321</v>
+      </c>
+      <c r="D75">
+        <v>26.94410533450321</v>
+      </c>
+      <c r="E75">
+        <v>43.74699999999999</v>
+      </c>
+      <c r="F75">
+        <v>178.047</v>
+      </c>
+      <c r="G75">
+        <v>165</v>
+      </c>
+      <c r="H75">
+        <v>109.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>43.9</v>
+      </c>
+      <c r="K75">
+        <v>32</v>
+      </c>
+      <c r="L75">
+        <v>11.9</v>
+      </c>
+      <c r="M75">
+        <v>42.5176236</v>
+      </c>
+      <c r="N75">
+        <v>-30.6176236</v>
+      </c>
+      <c r="O75">
+        <v>-7.348229664</v>
+      </c>
+      <c r="P75">
+        <v>-23.269393936</v>
+      </c>
+      <c r="Q75">
+        <v>8.730606064</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3122270316959834</v>
+      </c>
+      <c r="T75">
+        <v>4.140350800742537</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.06717214552884841</v>
+      </c>
+      <c r="W75">
+        <v>0.222759291647711</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2798839397035351</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2489155814607446</v>
+      </c>
+      <c r="C76">
+        <v>11.20163596514769</v>
+      </c>
+      <c r="D76">
+        <v>26.68763596514768</v>
+      </c>
+      <c r="E76">
+        <v>46.18599999999998</v>
+      </c>
+      <c r="F76">
+        <v>180.486</v>
+      </c>
+      <c r="G76">
+        <v>165</v>
+      </c>
+      <c r="H76">
+        <v>109.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>43.9</v>
+      </c>
+      <c r="K76">
+        <v>32</v>
+      </c>
+      <c r="L76">
+        <v>11.9</v>
+      </c>
+      <c r="M76">
+        <v>43.1000568</v>
+      </c>
+      <c r="N76">
+        <v>-31.2000568</v>
+      </c>
+      <c r="O76">
+        <v>-7.488013631999999</v>
+      </c>
+      <c r="P76">
+        <v>-23.712043168</v>
+      </c>
+      <c r="Q76">
+        <v>8.287956831999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3227434559919827</v>
+      </c>
+      <c r="T76">
+        <v>4.299595062309558</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.06626441383251262</v>
+      </c>
+      <c r="W76">
+        <v>0.222976057976796</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.276101724302136</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2509155814607446</v>
+      </c>
+      <c r="C77">
+        <v>8.511003003708794</v>
+      </c>
+      <c r="D77">
+        <v>26.43600300370881</v>
+      </c>
+      <c r="E77">
+        <v>48.625</v>
+      </c>
+      <c r="F77">
+        <v>182.925</v>
+      </c>
+      <c r="G77">
+        <v>165</v>
+      </c>
+      <c r="H77">
+        <v>109.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>43.9</v>
+      </c>
+      <c r="K77">
+        <v>32</v>
+      </c>
+      <c r="L77">
+        <v>11.9</v>
+      </c>
+      <c r="M77">
+        <v>43.68249000000001</v>
+      </c>
+      <c r="N77">
+        <v>-31.78249000000001</v>
+      </c>
+      <c r="O77">
+        <v>-7.627797600000002</v>
+      </c>
+      <c r="P77">
+        <v>-24.15469240000001</v>
+      </c>
+      <c r="Q77">
+        <v>7.845307599999991</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3341011942316621</v>
+      </c>
+      <c r="T77">
+        <v>4.47157886480194</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06538088831474577</v>
+      </c>
+      <c r="W77">
+        <v>0.2231870438704387</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2724203679781074</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2529155814607446</v>
+      </c>
+      <c r="C78">
+        <v>5.825070923162798</v>
+      </c>
+      <c r="D78">
+        <v>26.18907092316281</v>
+      </c>
+      <c r="E78">
+        <v>51.06399999999999</v>
+      </c>
+      <c r="F78">
+        <v>185.364</v>
+      </c>
+      <c r="G78">
+        <v>165</v>
+      </c>
+      <c r="H78">
+        <v>109.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>43.9</v>
+      </c>
+      <c r="K78">
+        <v>32</v>
+      </c>
+      <c r="L78">
+        <v>11.9</v>
+      </c>
+      <c r="M78">
+        <v>44.26492320000001</v>
+      </c>
+      <c r="N78">
+        <v>-32.36492320000001</v>
+      </c>
+      <c r="O78">
+        <v>-7.767581568000002</v>
+      </c>
+      <c r="P78">
+        <v>-24.59734163200001</v>
+      </c>
+      <c r="Q78">
+        <v>7.402658367999994</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3464054106579813</v>
+      </c>
+      <c r="T78">
+        <v>4.657894650835354</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06452061346849913</v>
+      </c>
+      <c r="W78">
+        <v>0.2233924775037224</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2688358894520797</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2549155814607446</v>
+      </c>
+      <c r="C79">
+        <v>3.14370921332079</v>
+      </c>
+      <c r="D79">
+        <v>25.9467092133208</v>
+      </c>
+      <c r="E79">
+        <v>53.50299999999999</v>
+      </c>
+      <c r="F79">
+        <v>187.803</v>
+      </c>
+      <c r="G79">
+        <v>165</v>
+      </c>
+      <c r="H79">
+        <v>109.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>43.9</v>
+      </c>
+      <c r="K79">
+        <v>32</v>
+      </c>
+      <c r="L79">
+        <v>11.9</v>
+      </c>
+      <c r="M79">
+        <v>44.8473564</v>
+      </c>
+      <c r="N79">
+        <v>-32.9473564</v>
+      </c>
+      <c r="O79">
+        <v>-7.907365536</v>
+      </c>
+      <c r="P79">
+        <v>-25.039990864</v>
+      </c>
+      <c r="Q79">
+        <v>6.960009135999996</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3597795589474588</v>
+      </c>
+      <c r="T79">
+        <v>4.860411809567326</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06368268342345369</v>
+      </c>
+      <c r="W79">
+        <v>0.2235925751984792</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2653445142643903</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2569155814607446</v>
+      </c>
+      <c r="C80">
+        <v>0.4667921508206803</v>
+      </c>
+      <c r="D80">
+        <v>25.70879215082071</v>
+      </c>
+      <c r="E80">
+        <v>55.94200000000001</v>
+      </c>
+      <c r="F80">
+        <v>190.242</v>
+      </c>
+      <c r="G80">
+        <v>165</v>
+      </c>
+      <c r="H80">
+        <v>109.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>43.9</v>
+      </c>
+      <c r="K80">
+        <v>32</v>
+      </c>
+      <c r="L80">
+        <v>11.9</v>
+      </c>
+      <c r="M80">
+        <v>45.42978960000001</v>
+      </c>
+      <c r="N80">
+        <v>-33.52978960000001</v>
+      </c>
+      <c r="O80">
+        <v>-8.047149504000002</v>
+      </c>
+      <c r="P80">
+        <v>-25.482640096</v>
+      </c>
+      <c r="Q80">
+        <v>6.517359903999996</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3743695388996161</v>
+      </c>
+      <c r="T80">
+        <v>5.081339619093114</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06286623876417863</v>
+      </c>
+      <c r="W80">
+        <v>0.2237875421831142</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.261942661517411</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2589155814607446</v>
+      </c>
+      <c r="C81">
+        <v>-2.205801418341565</v>
+      </c>
+      <c r="D81">
+        <v>25.47519858165844</v>
+      </c>
+      <c r="E81">
+        <v>58.381</v>
+      </c>
+      <c r="F81">
+        <v>192.681</v>
+      </c>
+      <c r="G81">
+        <v>165</v>
+      </c>
+      <c r="H81">
+        <v>109.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>43.9</v>
+      </c>
+      <c r="K81">
+        <v>32</v>
+      </c>
+      <c r="L81">
+        <v>11.9</v>
+      </c>
+      <c r="M81">
+        <v>46.0122228</v>
+      </c>
+      <c r="N81">
+        <v>-34.1122228</v>
+      </c>
+      <c r="O81">
+        <v>-8.186933472000002</v>
+      </c>
+      <c r="P81">
+        <v>-25.92528932800001</v>
+      </c>
+      <c r="Q81">
+        <v>6.074710671999995</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3903490407519787</v>
+      </c>
+      <c r="T81">
+        <v>5.323308172383263</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06207046358994852</v>
+      </c>
+      <c r="W81">
+        <v>0.2239775732947203</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2586269316247856</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2609155814607446</v>
+      </c>
+      <c r="C82">
+        <v>-4.874188284531868</v>
+      </c>
+      <c r="D82">
+        <v>25.24581171546814</v>
+      </c>
+      <c r="E82">
+        <v>60.81999999999999</v>
+      </c>
+      <c r="F82">
+        <v>195.12</v>
+      </c>
+      <c r="G82">
+        <v>165</v>
+      </c>
+      <c r="H82">
+        <v>109.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>43.9</v>
+      </c>
+      <c r="K82">
+        <v>32</v>
+      </c>
+      <c r="L82">
+        <v>11.9</v>
+      </c>
+      <c r="M82">
+        <v>46.594656</v>
+      </c>
+      <c r="N82">
+        <v>-34.694656</v>
+      </c>
+      <c r="O82">
+        <v>-8.326717439999999</v>
+      </c>
+      <c r="P82">
+        <v>-26.36793856</v>
+      </c>
+      <c r="Q82">
+        <v>5.632061439999998</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4079264927895777</v>
+      </c>
+      <c r="T82">
+        <v>5.589473581002427</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06129458279507417</v>
+      </c>
+      <c r="W82">
+        <v>0.2241628536285363</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2553940949794757</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2629155814607446</v>
+      </c>
+      <c r="C83">
+        <v>-7.538481069182751</v>
+      </c>
+      <c r="D83">
+        <v>25.02051893081729</v>
+      </c>
+      <c r="E83">
+        <v>63.25900000000001</v>
+      </c>
+      <c r="F83">
+        <v>197.559</v>
+      </c>
+      <c r="G83">
+        <v>165</v>
+      </c>
+      <c r="H83">
+        <v>109.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>43.9</v>
+      </c>
+      <c r="K83">
+        <v>32</v>
+      </c>
+      <c r="L83">
+        <v>11.9</v>
+      </c>
+      <c r="M83">
+        <v>47.17708920000001</v>
+      </c>
+      <c r="N83">
+        <v>-35.27708920000001</v>
+      </c>
+      <c r="O83">
+        <v>-8.466501408000003</v>
+      </c>
+      <c r="P83">
+        <v>-26.81058779200001</v>
+      </c>
+      <c r="Q83">
+        <v>5.18941220799999</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4273542029363975</v>
+      </c>
+      <c r="T83">
+        <v>5.883656401055186</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06053785955069053</v>
+      </c>
+      <c r="W83">
+        <v>0.2243435591392951</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2522410814612105</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2649155814607446</v>
+      </c>
+      <c r="C84">
+        <v>-10.19878840916508</v>
+      </c>
+      <c r="D84">
+        <v>24.79921159083496</v>
+      </c>
+      <c r="E84">
+        <v>65.69800000000001</v>
+      </c>
+      <c r="F84">
+        <v>199.998</v>
+      </c>
+      <c r="G84">
+        <v>165</v>
+      </c>
+      <c r="H84">
+        <v>109.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>43.9</v>
+      </c>
+      <c r="K84">
+        <v>32</v>
+      </c>
+      <c r="L84">
+        <v>11.9</v>
+      </c>
+      <c r="M84">
+        <v>47.75952240000001</v>
+      </c>
+      <c r="N84">
+        <v>-35.85952240000001</v>
+      </c>
+      <c r="O84">
+        <v>-8.606285376000002</v>
+      </c>
+      <c r="P84">
+        <v>-27.25323702400001</v>
+      </c>
+      <c r="Q84">
+        <v>4.746762975999992</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4489405475439752</v>
+      </c>
+      <c r="T84">
+        <v>6.210526201113807</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05979959297080406</v>
+      </c>
+      <c r="W84">
+        <v>0.224519857198572</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2491649707116836</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2669155814607446</v>
+      </c>
+      <c r="C85">
+        <v>-12.85521513146111</v>
+      </c>
+      <c r="D85">
+        <v>24.5817848685389</v>
+      </c>
+      <c r="E85">
+        <v>68.137</v>
+      </c>
+      <c r="F85">
+        <v>202.437</v>
+      </c>
+      <c r="G85">
+        <v>165</v>
+      </c>
+      <c r="H85">
+        <v>109.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>43.9</v>
+      </c>
+      <c r="K85">
+        <v>32</v>
+      </c>
+      <c r="L85">
+        <v>11.9</v>
+      </c>
+      <c r="M85">
+        <v>48.34195560000001</v>
+      </c>
+      <c r="N85">
+        <v>-36.44195560000001</v>
+      </c>
+      <c r="O85">
+        <v>-8.746069344000002</v>
+      </c>
+      <c r="P85">
+        <v>-27.695886256</v>
+      </c>
+      <c r="Q85">
+        <v>4.304113743999995</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4730664621053856</v>
+      </c>
+      <c r="T85">
+        <v>6.575851271767561</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05907911594705943</v>
+      </c>
+      <c r="W85">
+        <v>0.2246919071118422</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2461629831127476</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2689155814607446</v>
+      </c>
+      <c r="C86">
+        <v>-15.50786241872865</v>
+      </c>
+      <c r="D86">
+        <v>24.36813758127137</v>
+      </c>
+      <c r="E86">
+        <v>70.57599999999999</v>
+      </c>
+      <c r="F86">
+        <v>204.876</v>
+      </c>
+      <c r="G86">
+        <v>165</v>
+      </c>
+      <c r="H86">
+        <v>109.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>43.9</v>
+      </c>
+      <c r="K86">
+        <v>32</v>
+      </c>
+      <c r="L86">
+        <v>11.9</v>
+      </c>
+      <c r="M86">
+        <v>48.9243888</v>
+      </c>
+      <c r="N86">
+        <v>-37.0243888</v>
+      </c>
+      <c r="O86">
+        <v>-8.885853312</v>
+      </c>
+      <c r="P86">
+        <v>-28.138535488</v>
+      </c>
+      <c r="Q86">
+        <v>3.861464511999998</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5002081159869719</v>
+      </c>
+      <c r="T86">
+        <v>6.98684197625303</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05837579313816588</v>
+      </c>
+      <c r="W86">
+        <v>0.224859860598606</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2432324714090245</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2709155814607446</v>
+      </c>
+      <c r="C87">
+        <v>-18.15682796630554</v>
+      </c>
+      <c r="D87">
+        <v>24.15817203369444</v>
+      </c>
+      <c r="E87">
+        <v>73.01499999999999</v>
+      </c>
+      <c r="F87">
+        <v>207.315</v>
+      </c>
+      <c r="G87">
+        <v>165</v>
+      </c>
+      <c r="H87">
+        <v>109.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>43.9</v>
+      </c>
+      <c r="K87">
+        <v>32</v>
+      </c>
+      <c r="L87">
+        <v>11.9</v>
+      </c>
+      <c r="M87">
+        <v>49.506822</v>
+      </c>
+      <c r="N87">
+        <v>-37.606822</v>
+      </c>
+      <c r="O87">
+        <v>-9.02563728</v>
+      </c>
+      <c r="P87">
+        <v>-28.58118472</v>
+      </c>
+      <c r="Q87">
+        <v>3.418815279999997</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5309686570527701</v>
+      </c>
+      <c r="T87">
+        <v>7.452631441336567</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05768901910124628</v>
+      </c>
+      <c r="W87">
+        <v>0.2250238622386224</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2403709129218595</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2729155814607446</v>
+      </c>
+      <c r="C88">
+        <v>-20.8022061311672</v>
+      </c>
+      <c r="D88">
+        <v>23.95179386883278</v>
+      </c>
+      <c r="E88">
+        <v>75.45399999999998</v>
+      </c>
+      <c r="F88">
+        <v>209.754</v>
+      </c>
+      <c r="G88">
+        <v>165</v>
+      </c>
+      <c r="H88">
+        <v>109.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>43.9</v>
+      </c>
+      <c r="K88">
+        <v>32</v>
+      </c>
+      <c r="L88">
+        <v>11.9</v>
+      </c>
+      <c r="M88">
+        <v>50.0892552</v>
+      </c>
+      <c r="N88">
+        <v>-38.18925520000001</v>
+      </c>
+      <c r="O88">
+        <v>-9.165421248000001</v>
+      </c>
+      <c r="P88">
+        <v>-29.023833952</v>
+      </c>
+      <c r="Q88">
+        <v>2.976166047999996</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.566123561127968</v>
+      </c>
+      <c r="T88">
+        <v>7.984962258574893</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.05701821655355736</v>
+      </c>
+      <c r="W88">
+        <v>0.2251840498870105</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2375759023064891</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2749155814607446</v>
+      </c>
+      <c r="C89">
+        <v>-23.44408807331314</v>
+      </c>
+      <c r="D89">
+        <v>23.74891192668688</v>
+      </c>
+      <c r="E89">
+        <v>77.893</v>
+      </c>
+      <c r="F89">
+        <v>212.193</v>
+      </c>
+      <c r="G89">
+        <v>165</v>
+      </c>
+      <c r="H89">
+        <v>109.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>43.9</v>
+      </c>
+      <c r="K89">
+        <v>32</v>
+      </c>
+      <c r="L89">
+        <v>11.9</v>
+      </c>
+      <c r="M89">
+        <v>50.67168840000001</v>
+      </c>
+      <c r="N89">
+        <v>-38.77168840000001</v>
+      </c>
+      <c r="O89">
+        <v>-9.305205216000003</v>
+      </c>
+      <c r="P89">
+        <v>-29.466483184</v>
+      </c>
+      <c r="Q89">
+        <v>2.533516815999995</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6066869119839655</v>
+      </c>
+      <c r="T89">
+        <v>8.599190124619115</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.05636283475409118</v>
+      </c>
+      <c r="W89">
+        <v>0.225340555060723</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2348451448087133</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2769155814607445</v>
+      </c>
+      <c r="C90">
+        <v>-26.0825618900285</v>
+      </c>
+      <c r="D90">
+        <v>23.54943810997151</v>
+      </c>
+      <c r="E90">
+        <v>80.33199999999999</v>
+      </c>
+      <c r="F90">
+        <v>214.632</v>
+      </c>
+      <c r="G90">
+        <v>165</v>
+      </c>
+      <c r="H90">
+        <v>109.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>43.9</v>
+      </c>
+      <c r="K90">
+        <v>32</v>
+      </c>
+      <c r="L90">
+        <v>11.9</v>
+      </c>
+      <c r="M90">
+        <v>51.2541216</v>
+      </c>
+      <c r="N90">
+        <v>-39.35412160000001</v>
+      </c>
+      <c r="O90">
+        <v>-9.444989184000001</v>
+      </c>
+      <c r="P90">
+        <v>-29.90913241600001</v>
+      </c>
+      <c r="Q90">
+        <v>2.090867583999994</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6540108213159626</v>
+      </c>
+      <c r="T90">
+        <v>9.315789301670709</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05572234799552197</v>
+      </c>
+      <c r="W90">
+        <v>0.2254935032986694</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2321764499813416</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2789155814607446</v>
+      </c>
+      <c r="C91">
+        <v>-28.7177127434359</v>
+      </c>
+      <c r="D91">
+        <v>23.35328725656409</v>
+      </c>
+      <c r="E91">
+        <v>82.77099999999999</v>
+      </c>
+      <c r="F91">
+        <v>217.071</v>
+      </c>
+      <c r="G91">
+        <v>165</v>
+      </c>
+      <c r="H91">
+        <v>109.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>43.9</v>
+      </c>
+      <c r="K91">
+        <v>32</v>
+      </c>
+      <c r="L91">
+        <v>11.9</v>
+      </c>
+      <c r="M91">
+        <v>51.8365548</v>
+      </c>
+      <c r="N91">
+        <v>-39.9365548</v>
+      </c>
+      <c r="O91">
+        <v>-9.584773152</v>
+      </c>
+      <c r="P91">
+        <v>-30.351781648</v>
+      </c>
+      <c r="Q91">
+        <v>1.648218351999997</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.709939077799232</v>
+      </c>
+      <c r="T91">
+        <v>10.16267923818623</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05509625419781948</v>
+      </c>
+      <c r="W91">
+        <v>0.2256430144975607</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2295677258242478</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2809155814607446</v>
+      </c>
+      <c r="C92">
+        <v>-31.34962298172516</v>
+      </c>
+      <c r="D92">
+        <v>23.16037701827486</v>
+      </c>
+      <c r="E92">
+        <v>85.21000000000001</v>
+      </c>
+      <c r="F92">
+        <v>219.51</v>
+      </c>
+      <c r="G92">
+        <v>165</v>
+      </c>
+      <c r="H92">
+        <v>109.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>43.9</v>
+      </c>
+      <c r="K92">
+        <v>32</v>
+      </c>
+      <c r="L92">
+        <v>11.9</v>
+      </c>
+      <c r="M92">
+        <v>52.41898800000001</v>
+      </c>
+      <c r="N92">
+        <v>-40.51898800000001</v>
+      </c>
+      <c r="O92">
+        <v>-9.724557120000002</v>
+      </c>
+      <c r="P92">
+        <v>-30.79443088000001</v>
+      </c>
+      <c r="Q92">
+        <v>1.205569119999993</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7770529855791553</v>
+      </c>
+      <c r="T92">
+        <v>11.17894716200485</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05448407359562148</v>
+      </c>
+      <c r="W92">
+        <v>0.2257892032253656</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2270169733150895</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2829155814607446</v>
+      </c>
+      <c r="C93">
+        <v>-33.97837225442368</v>
+      </c>
+      <c r="D93">
+        <v>22.97062774557635</v>
+      </c>
+      <c r="E93">
+        <v>87.649</v>
+      </c>
+      <c r="F93">
+        <v>221.949</v>
+      </c>
+      <c r="G93">
+        <v>165</v>
+      </c>
+      <c r="H93">
+        <v>109.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>43.9</v>
+      </c>
+      <c r="K93">
+        <v>32</v>
+      </c>
+      <c r="L93">
+        <v>11.9</v>
+      </c>
+      <c r="M93">
+        <v>53.0014212</v>
+      </c>
+      <c r="N93">
+        <v>-41.1014212</v>
+      </c>
+      <c r="O93">
+        <v>-9.864341088000002</v>
+      </c>
+      <c r="P93">
+        <v>-31.237080112</v>
+      </c>
+      <c r="Q93">
+        <v>0.762919887999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8590810950879504</v>
+      </c>
+      <c r="T93">
+        <v>12.42105240222761</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05388534751215311</v>
+      </c>
+      <c r="W93">
+        <v>0.2259321790140978</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.224522281300638</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2849155814607446</v>
+      </c>
+      <c r="C94">
+        <v>-36.60403762204677</v>
+      </c>
+      <c r="D94">
+        <v>22.78396237795322</v>
+      </c>
+      <c r="E94">
+        <v>90.08799999999999</v>
+      </c>
+      <c r="F94">
+        <v>224.388</v>
+      </c>
+      <c r="G94">
+        <v>165</v>
+      </c>
+      <c r="H94">
+        <v>109.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>43.9</v>
+      </c>
+      <c r="K94">
+        <v>32</v>
+      </c>
+      <c r="L94">
+        <v>11.9</v>
+      </c>
+      <c r="M94">
+        <v>53.58385440000001</v>
+      </c>
+      <c r="N94">
+        <v>-41.68385440000001</v>
+      </c>
+      <c r="O94">
+        <v>-10.004125056</v>
+      </c>
+      <c r="P94">
+        <v>-31.67972934400001</v>
+      </c>
+      <c r="Q94">
+        <v>0.320270655999991</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9616162319739447</v>
+      </c>
+      <c r="T94">
+        <v>13.97368395250607</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05329963721310797</v>
+      </c>
+      <c r="W94">
+        <v>0.2260720466335098</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2220818217212832</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2869155814607446</v>
+      </c>
+      <c r="C95">
+        <v>-39.22669366044485</v>
+      </c>
+      <c r="D95">
+        <v>22.60030633955517</v>
+      </c>
+      <c r="E95">
+        <v>92.52700000000002</v>
+      </c>
+      <c r="F95">
+        <v>226.827</v>
+      </c>
+      <c r="G95">
+        <v>165</v>
+      </c>
+      <c r="H95">
+        <v>109.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>43.9</v>
+      </c>
+      <c r="K95">
+        <v>32</v>
+      </c>
+      <c r="L95">
+        <v>11.9</v>
+      </c>
+      <c r="M95">
+        <v>54.16628760000001</v>
+      </c>
+      <c r="N95">
+        <v>-42.26628760000001</v>
+      </c>
+      <c r="O95">
+        <v>-10.143909024</v>
+      </c>
+      <c r="P95">
+        <v>-32.12237857600001</v>
+      </c>
+      <c r="Q95">
+        <v>-0.1223785760000098</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.093447122255937</v>
+      </c>
+      <c r="T95">
+        <v>15.9699245171498</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0527265228344724</v>
+      </c>
+      <c r="W95">
+        <v>0.226208906347128</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.219693845143635</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2889155814607446</v>
+      </c>
+      <c r="C96">
+        <v>-41.84641256014365</v>
+      </c>
+      <c r="D96">
+        <v>22.41958743985638</v>
+      </c>
+      <c r="E96">
+        <v>94.96600000000001</v>
+      </c>
+      <c r="F96">
+        <v>229.266</v>
+      </c>
+      <c r="G96">
+        <v>165</v>
+      </c>
+      <c r="H96">
+        <v>109.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>43.9</v>
+      </c>
+      <c r="K96">
+        <v>32</v>
+      </c>
+      <c r="L96">
+        <v>11.9</v>
+      </c>
+      <c r="M96">
+        <v>54.74872080000001</v>
+      </c>
+      <c r="N96">
+        <v>-42.84872080000001</v>
+      </c>
+      <c r="O96">
+        <v>-10.283692992</v>
+      </c>
+      <c r="P96">
+        <v>-32.56502780800001</v>
+      </c>
+      <c r="Q96">
+        <v>-0.5650278080000106</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.269221642631926</v>
+      </c>
+      <c r="T96">
+        <v>18.63157860334143</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05216560237878652</v>
+      </c>
+      <c r="W96">
+        <v>0.2263428541519458</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2173566765782772</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2909155814607445</v>
+      </c>
+      <c r="C97">
+        <v>-44.46326422095697</v>
+      </c>
+      <c r="D97">
+        <v>22.24173577904304</v>
+      </c>
+      <c r="E97">
+        <v>97.405</v>
+      </c>
+      <c r="F97">
+        <v>231.705</v>
+      </c>
+      <c r="G97">
+        <v>165</v>
+      </c>
+      <c r="H97">
+        <v>109.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>43.9</v>
+      </c>
+      <c r="K97">
+        <v>32</v>
+      </c>
+      <c r="L97">
+        <v>11.9</v>
+      </c>
+      <c r="M97">
+        <v>55.33115400000001</v>
+      </c>
+      <c r="N97">
+        <v>-43.43115400000001</v>
+      </c>
+      <c r="O97">
+        <v>-10.42347696</v>
+      </c>
+      <c r="P97">
+        <v>-33.00767704</v>
+      </c>
+      <c r="Q97">
+        <v>-1.007677040000004</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.515305971158312</v>
+      </c>
+      <c r="T97">
+        <v>22.35789432400973</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0516164907747993</v>
+      </c>
+      <c r="W97">
+        <v>0.2264739820029779</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2150687115616637</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2929155814607446</v>
+      </c>
+      <c r="C98">
+        <v>-47.07731634213104</v>
+      </c>
+      <c r="D98">
+        <v>22.06668365786897</v>
+      </c>
+      <c r="E98">
+        <v>99.84399999999999</v>
+      </c>
+      <c r="F98">
+        <v>234.144</v>
+      </c>
+      <c r="G98">
+        <v>165</v>
+      </c>
+      <c r="H98">
+        <v>109.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>43.9</v>
+      </c>
+      <c r="K98">
+        <v>32</v>
+      </c>
+      <c r="L98">
+        <v>11.9</v>
+      </c>
+      <c r="M98">
+        <v>55.9135872</v>
+      </c>
+      <c r="N98">
+        <v>-44.0135872</v>
+      </c>
+      <c r="O98">
+        <v>-10.563260928</v>
+      </c>
+      <c r="P98">
+        <v>-33.45032627200001</v>
+      </c>
+      <c r="Q98">
+        <v>-1.450326272000005</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.884432463947886</v>
+      </c>
+      <c r="T98">
+        <v>27.9473679050121</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05107881899589514</v>
+      </c>
+      <c r="W98">
+        <v>0.2266023780237802</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2128284124828964</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2949155814607446</v>
+      </c>
+      <c r="C99">
+        <v>-49.68863450826532</v>
+      </c>
+      <c r="D99">
+        <v>21.89436549173466</v>
+      </c>
+      <c r="E99">
+        <v>102.283</v>
+      </c>
+      <c r="F99">
+        <v>236.583</v>
+      </c>
+      <c r="G99">
+        <v>165</v>
+      </c>
+      <c r="H99">
+        <v>109.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>43.9</v>
+      </c>
+      <c r="K99">
+        <v>32</v>
+      </c>
+      <c r="L99">
+        <v>11.9</v>
+      </c>
+      <c r="M99">
+        <v>56.4960204</v>
+      </c>
+      <c r="N99">
+        <v>-44.5960204</v>
+      </c>
+      <c r="O99">
+        <v>-10.703044896</v>
+      </c>
+      <c r="P99">
+        <v>-33.892975504</v>
+      </c>
+      <c r="Q99">
+        <v>-1.892975503999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.499643285263849</v>
+      </c>
+      <c r="T99">
+        <v>37.26315720668281</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05055223323305087</v>
+      </c>
+      <c r="W99">
+        <v>0.2267281267039475</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.210634305137712</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2969155814607446</v>
+      </c>
+      <c r="C100">
+        <v>-52.29728227123903</v>
+      </c>
+      <c r="D100">
+        <v>21.72471772876096</v>
+      </c>
+      <c r="E100">
+        <v>104.722</v>
+      </c>
+      <c r="F100">
+        <v>239.022</v>
+      </c>
+      <c r="G100">
+        <v>165</v>
+      </c>
+      <c r="H100">
+        <v>109.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>43.9</v>
+      </c>
+      <c r="K100">
+        <v>32</v>
+      </c>
+      <c r="L100">
+        <v>11.9</v>
+      </c>
+      <c r="M100">
+        <v>57.0784536</v>
+      </c>
+      <c r="N100">
+        <v>-45.1784536</v>
+      </c>
+      <c r="O100">
+        <v>-10.842828864</v>
+      </c>
+      <c r="P100">
+        <v>-34.335624736</v>
+      </c>
+      <c r="Q100">
+        <v>-2.335624736</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.730064927895773</v>
+      </c>
+      <c r="T100">
+        <v>55.89473581002421</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0500363941184279</v>
+      </c>
+      <c r="W100">
+        <v>0.2268513090845194</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2084849754934496</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2989155814607446</v>
+      </c>
+      <c r="C101">
+        <v>-54.90332122835773</v>
+      </c>
+      <c r="D101">
+        <v>21.55767877164229</v>
+      </c>
+      <c r="E101">
+        <v>107.161</v>
+      </c>
+      <c r="F101">
+        <v>241.461</v>
+      </c>
+      <c r="G101">
+        <v>165</v>
+      </c>
+      <c r="H101">
+        <v>109.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>43.9</v>
+      </c>
+      <c r="K101">
+        <v>32</v>
+      </c>
+      <c r="L101">
+        <v>11.9</v>
+      </c>
+      <c r="M101">
+        <v>57.66088680000001</v>
+      </c>
+      <c r="N101">
+        <v>-45.76088680000001</v>
+      </c>
+      <c r="O101">
+        <v>-10.982612832</v>
+      </c>
+      <c r="P101">
+        <v>-34.77827396800001</v>
+      </c>
+      <c r="Q101">
+        <v>-2.778273968000008</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.421329855791546</v>
+      </c>
+      <c r="T101">
+        <v>111.7894716200484</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04953097599601953</v>
+      </c>
+      <c r="W101">
+        <v>0.2269720029321506</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2063790666500813</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
